--- a/data/output/sim_gridrnd/ABS1/group_480_40/results/ABS1_G2_results_summary.xlsx
+++ b/data/output/sim_gridrnd/ABS1/group_480_40/results/ABS1_G2_results_summary.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CM23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,24 +436,24 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>mu</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sigma</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>jnd</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>pse</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>jnd</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>sigma</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>mu</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>n_trials</t>
@@ -466,384 +466,439 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>lat_entropy_100</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_120</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_140</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_160</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_180</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_200</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_40</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_60</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_80</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>model</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>pse_40</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>jnd_40</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>pse_60</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>jnd_60</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>pse_80</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>jnd_80</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>pse_100</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>jnd_100</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pse_120</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>jnd_120</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>pse_140</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>jnd_140</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>pse_160</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>jnd_160</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>pse_180</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>jnd_180</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>pse_200</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>jnd_200</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_40</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_60</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_80</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_100</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_120</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_140</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_160</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_180</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_200</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_40</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_60</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_80</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_100</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_120</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_140</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_160</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_180</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_200</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_40</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_60</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_80</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_100</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_120</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_140</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_160</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_180</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_200</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_40</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_60</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_80</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_100</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_120</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_140</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_160</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_180</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_200</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_40</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_60</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_80</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_100</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_120</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_140</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_160</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_180</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_200</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_40</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_60</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_80</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_100</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_120</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_140</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_160</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_180</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_200</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>pse_est</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>jnd_est</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S02_G2_481_41_ABS1</t>
+          <t>S01_G2_481_40_ABS1</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>481</v>
       </c>
       <c r="C2" t="n">
-        <v>41</v>
+        <v>59.30318754633062</v>
       </c>
       <c r="D2" t="n">
-        <v>60.78576723498888</v>
+        <v>40</v>
       </c>
       <c r="E2" t="n">
         <v>481</v>
@@ -852,736 +907,835 @@
         <v>200</v>
       </c>
       <c r="G2" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="H2" t="inlineStr">
+        <v>72.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>461.6053564640781</v>
-      </c>
-      <c r="J2" t="n">
-        <v>61.1643644444494</v>
-      </c>
-      <c r="K2" t="n">
-        <v>474.6051324069251</v>
-      </c>
-      <c r="L2" t="n">
-        <v>67.38313607459806</v>
-      </c>
-      <c r="M2" t="n">
-        <v>476.6170093611837</v>
-      </c>
-      <c r="N2" t="n">
-        <v>65.20756885311297</v>
-      </c>
-      <c r="O2" t="n">
-        <v>479.9957501997357</v>
-      </c>
-      <c r="P2" t="n">
-        <v>56.13507627925839</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>472.7860101523429</v>
-      </c>
       <c r="R2" t="n">
-        <v>59.13725021697132</v>
+        <v>462.57</v>
       </c>
       <c r="S2" t="n">
-        <v>477.791639314418</v>
+        <v>24.53</v>
       </c>
       <c r="T2" t="n">
-        <v>60.88523493298758</v>
+        <v>474.48</v>
       </c>
       <c r="U2" t="n">
-        <v>476.3342570674745</v>
+        <v>41.24</v>
       </c>
       <c r="V2" t="n">
-        <v>58.54379140810553</v>
+        <v>475.15</v>
       </c>
       <c r="W2" t="n">
-        <v>476.3531437705406</v>
+        <v>39.13</v>
       </c>
       <c r="X2" t="n">
-        <v>54.32221112550808</v>
+        <v>476.25</v>
       </c>
       <c r="Y2" t="n">
-        <v>471.0838637043079</v>
+        <v>41.61</v>
       </c>
       <c r="Z2" t="n">
-        <v>53.09244606274586</v>
+        <v>479.56</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.3333333333333333</v>
+        <v>44.22</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.1186440677966102</v>
+        <v>478.44</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.08860759493670886</v>
+        <v>45.88</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.1111111111111111</v>
+        <v>480.18</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.09243697478991597</v>
+        <v>43.07</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.06474820143884892</v>
+        <v>480.9</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.05660377358490566</v>
+        <v>46.05</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0.05027932960893855</v>
+        <v>481.86</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.01507537688442211</v>
+        <v>46.9</v>
       </c>
       <c r="AJ2" t="n">
-        <v>453.35</v>
+        <v>-0.85</v>
       </c>
       <c r="AK2" t="n">
-        <v>467.9</v>
+        <v>-0.4915254237288136</v>
       </c>
       <c r="AL2" t="n">
-        <v>471.7625</v>
+        <v>-0.3417721518987342</v>
       </c>
       <c r="AM2" t="n">
-        <v>471.39</v>
+        <v>-0.2525252525252525</v>
       </c>
       <c r="AN2" t="n">
-        <v>472.2083333333333</v>
+        <v>-0.1764705882352941</v>
       </c>
       <c r="AO2" t="n">
-        <v>473.2142857142857</v>
+        <v>-0.1654676258992806</v>
       </c>
       <c r="AP2" t="n">
-        <v>474</v>
+        <v>-0.1320754716981132</v>
       </c>
       <c r="AQ2" t="n">
-        <v>474.2888888888889</v>
+        <v>-0.106145251396648</v>
       </c>
       <c r="AR2" t="n">
-        <v>476.03</v>
+        <v>-0.09547738693467336</v>
       </c>
       <c r="AS2" t="n">
-        <v>64.51920256791772</v>
+        <v>458.225</v>
       </c>
       <c r="AT2" t="n">
-        <v>68.5666828714938</v>
+        <v>473.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>69.61523607479901</v>
+        <v>474.0375</v>
       </c>
       <c r="AV2" t="n">
-        <v>66.86596967067777</v>
+        <v>475.22</v>
       </c>
       <c r="AW2" t="n">
-        <v>63.89977775565595</v>
+        <v>476.7833333333334</v>
       </c>
       <c r="AX2" t="n">
-        <v>63.40378376657317</v>
+        <v>476.2071428571429</v>
       </c>
       <c r="AY2" t="n">
-        <v>63.18277059452205</v>
+        <v>476.8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>61.62426369980585</v>
+        <v>477.8</v>
       </c>
       <c r="BA2" t="n">
-        <v>60.16792417891779</v>
+        <v>478.075</v>
       </c>
       <c r="BB2" t="n">
-        <v>303</v>
+        <v>32.87893512570016</v>
       </c>
       <c r="BC2" t="n">
-        <v>303</v>
+        <v>40.79534287146022</v>
       </c>
       <c r="BD2" t="n">
-        <v>303</v>
+        <v>43.68278944561576</v>
       </c>
       <c r="BE2" t="n">
-        <v>303</v>
+        <v>43.97080394989385</v>
       </c>
       <c r="BF2" t="n">
-        <v>303</v>
+        <v>45.30786968679453</v>
       </c>
       <c r="BG2" t="n">
-        <v>303</v>
+        <v>46.29000145489172</v>
       </c>
       <c r="BH2" t="n">
-        <v>303</v>
+        <v>46.29036076765875</v>
       </c>
       <c r="BI2" t="n">
-        <v>303</v>
+        <v>46.2810736454739</v>
       </c>
       <c r="BJ2" t="n">
-        <v>303</v>
+        <v>46.31273447983827</v>
       </c>
       <c r="BK2" t="n">
-        <v>546</v>
+        <v>356</v>
       </c>
       <c r="BL2" t="n">
-        <v>570</v>
+        <v>356</v>
       </c>
       <c r="BM2" t="n">
-        <v>580</v>
+        <v>356</v>
       </c>
       <c r="BN2" t="n">
-        <v>580</v>
+        <v>356</v>
       </c>
       <c r="BO2" t="n">
-        <v>580</v>
+        <v>356</v>
       </c>
       <c r="BP2" t="n">
-        <v>580</v>
+        <v>356</v>
       </c>
       <c r="BQ2" t="n">
-        <v>580</v>
+        <v>356</v>
       </c>
       <c r="BR2" t="n">
-        <v>580</v>
+        <v>356</v>
       </c>
       <c r="BS2" t="n">
-        <v>580</v>
+        <v>356</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.5</v>
+        <v>519</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.7272727272727273</v>
+        <v>549</v>
       </c>
       <c r="BV2" t="n">
+        <v>549</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>549</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>549</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>549</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>549</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>549</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>549</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="CH2" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="BW2" t="n">
-        <v>0.9375</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>0.9411764705882353</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>0.9130434782608695</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>0.9629629629629629</v>
-      </c>
-      <c r="CA2" t="n">
+      <c r="CI2" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="CK2" t="n">
         <v>0.90625</v>
       </c>
-      <c r="CB2" t="n">
-        <v>0.8888888888888888</v>
+      <c r="CL2" t="n">
+        <v>481.86</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>46.9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S03_G2_482_42_ABS1</t>
+          <t>S02_G2_481_41_ABS1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C3" t="n">
-        <v>42</v>
+        <v>60.78576723498888</v>
       </c>
       <c r="D3" t="n">
-        <v>62.26834692364714</v>
+        <v>41</v>
       </c>
       <c r="E3" t="n">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F3" t="n">
         <v>200</v>
       </c>
       <c r="G3" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="H3" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>475.6021227681159</v>
-      </c>
-      <c r="J3" t="n">
-        <v>45.17493074020197</v>
-      </c>
-      <c r="K3" t="n">
-        <v>487.893762715605</v>
-      </c>
-      <c r="L3" t="n">
-        <v>59.2915958383588</v>
-      </c>
-      <c r="M3" t="n">
-        <v>488.1350129030637</v>
-      </c>
-      <c r="N3" t="n">
-        <v>51.08221091562601</v>
-      </c>
-      <c r="O3" t="n">
-        <v>491.2702456149453</v>
-      </c>
-      <c r="P3" t="n">
-        <v>46.54996563452494</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>488.1372789521262</v>
-      </c>
       <c r="R3" t="n">
-        <v>57.9688352785371</v>
+        <v>461.61</v>
       </c>
       <c r="S3" t="n">
-        <v>488.2188696973834</v>
+        <v>61.16</v>
       </c>
       <c r="T3" t="n">
-        <v>52.72485593829526</v>
+        <v>474.61</v>
       </c>
       <c r="U3" t="n">
-        <v>488.6003441236668</v>
+        <v>67.38</v>
       </c>
       <c r="V3" t="n">
-        <v>49.77290184461727</v>
+        <v>476.62</v>
       </c>
       <c r="W3" t="n">
-        <v>491.9535749077048</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>46.20105276236136</v>
+        <v>480</v>
       </c>
       <c r="Y3" t="n">
-        <v>492.3326847459285</v>
+        <v>56.14</v>
       </c>
       <c r="Z3" t="n">
-        <v>45.00040651398425</v>
+        <v>472.79</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.7894736842105263</v>
+        <v>59.14</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.2413793103448276</v>
+        <v>477.79</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.2051282051282051</v>
+        <v>60.89</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.1224489795918367</v>
+        <v>476.33</v>
       </c>
       <c r="AE3" t="n">
+        <v>58.54</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>476.35</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>54.32</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>471.08</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>53.09</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AK3" t="n">
         <v>-0.1186440677966102</v>
       </c>
-      <c r="AF3" t="n">
-        <v>-0.1014492753623188</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>-0.0759493670886076</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>-0.07865168539325842</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>-0.08080808080808081</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>460.3</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>486.8</v>
-      </c>
       <c r="AL3" t="n">
-        <v>484.6</v>
+        <v>-0.08860759493670886</v>
       </c>
       <c r="AM3" t="n">
-        <v>487.74</v>
+        <v>-0.1111111111111111</v>
       </c>
       <c r="AN3" t="n">
-        <v>487.5333333333334</v>
+        <v>-0.09243697478991597</v>
       </c>
       <c r="AO3" t="n">
-        <v>487.6428571428572</v>
+        <v>-0.06474820143884892</v>
       </c>
       <c r="AP3" t="n">
-        <v>487.85625</v>
+        <v>-0.05660377358490566</v>
       </c>
       <c r="AQ3" t="n">
-        <v>487.6722222222222</v>
+        <v>-0.05027932960893855</v>
       </c>
       <c r="AR3" t="n">
-        <v>487.62</v>
+        <v>-0.01507537688442211</v>
       </c>
       <c r="AS3" t="n">
-        <v>42.0417649486793</v>
+        <v>453.35</v>
       </c>
       <c r="AT3" t="n">
-        <v>57.13253597265455</v>
+        <v>467.9</v>
       </c>
       <c r="AU3" t="n">
-        <v>57.89594113579984</v>
+        <v>471.7625</v>
       </c>
       <c r="AV3" t="n">
-        <v>57.22492813451144</v>
+        <v>471.39</v>
       </c>
       <c r="AW3" t="n">
-        <v>56.34195200341887</v>
+        <v>472.2083333333333</v>
       </c>
       <c r="AX3" t="n">
-        <v>56.21846054564683</v>
+        <v>473.2142857142857</v>
       </c>
       <c r="AY3" t="n">
-        <v>55.57167071393032</v>
+        <v>474</v>
       </c>
       <c r="AZ3" t="n">
-        <v>54.20422600945383</v>
+        <v>474.2888888888889</v>
       </c>
       <c r="BA3" t="n">
-        <v>52.74983981018331</v>
+        <v>476.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>354</v>
+        <v>64.51920256791772</v>
       </c>
       <c r="BC3" t="n">
-        <v>354</v>
+        <v>68.5666828714938</v>
       </c>
       <c r="BD3" t="n">
-        <v>354</v>
+        <v>69.61523607479901</v>
       </c>
       <c r="BE3" t="n">
-        <v>354</v>
+        <v>66.86596967067777</v>
       </c>
       <c r="BF3" t="n">
-        <v>354</v>
+        <v>63.89977775565595</v>
       </c>
       <c r="BG3" t="n">
-        <v>354</v>
+        <v>63.40378376657317</v>
       </c>
       <c r="BH3" t="n">
-        <v>354</v>
+        <v>63.18277059452205</v>
       </c>
       <c r="BI3" t="n">
-        <v>354</v>
+        <v>61.62426369980585</v>
       </c>
       <c r="BJ3" t="n">
-        <v>354</v>
+        <v>60.16792417891779</v>
       </c>
       <c r="BK3" t="n">
-        <v>544</v>
+        <v>303</v>
       </c>
       <c r="BL3" t="n">
-        <v>573</v>
+        <v>303</v>
       </c>
       <c r="BM3" t="n">
-        <v>573</v>
+        <v>303</v>
       </c>
       <c r="BN3" t="n">
-        <v>573</v>
+        <v>303</v>
       </c>
       <c r="BO3" t="n">
-        <v>573</v>
+        <v>303</v>
       </c>
       <c r="BP3" t="n">
-        <v>573</v>
+        <v>303</v>
       </c>
       <c r="BQ3" t="n">
-        <v>573</v>
+        <v>303</v>
       </c>
       <c r="BR3" t="n">
-        <v>573</v>
+        <v>303</v>
       </c>
       <c r="BS3" t="n">
-        <v>573</v>
+        <v>303</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.5714285714285714</v>
+        <v>546</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.8</v>
+        <v>570</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.75</v>
+        <v>580</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.6923076923076923</v>
+        <v>580</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.25</v>
+        <v>580</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.6666666666666666</v>
+        <v>580</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.1666666666666667</v>
+        <v>580</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.32</v>
+        <v>580</v>
       </c>
       <c r="CB3" t="n">
-        <v>0</v>
+        <v>580</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>0.9130434782608695</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>0.9629629629629629</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>0.90625</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>471.08</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>53.09</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S01_G2_481_40_ABS1</t>
+          <t>S03_G2_482_42_ABS1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C4" t="n">
-        <v>40</v>
+        <v>62.26834692364714</v>
       </c>
       <c r="D4" t="n">
-        <v>59.30318754633062</v>
+        <v>42</v>
       </c>
       <c r="E4" t="n">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F4" t="n">
         <v>200</v>
       </c>
       <c r="G4" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="H4" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>462.5740873420312</v>
-      </c>
-      <c r="J4" t="n">
-        <v>24.52510941383181</v>
-      </c>
-      <c r="K4" t="n">
-        <v>474.482027997538</v>
-      </c>
-      <c r="L4" t="n">
-        <v>41.24444191444763</v>
-      </c>
-      <c r="M4" t="n">
-        <v>475.1506346140738</v>
-      </c>
-      <c r="N4" t="n">
-        <v>39.12510600450026</v>
-      </c>
-      <c r="O4" t="n">
-        <v>476.2481949328647</v>
-      </c>
-      <c r="P4" t="n">
-        <v>41.61215982770381</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>479.5556052055624</v>
-      </c>
       <c r="R4" t="n">
-        <v>44.21818287031817</v>
+        <v>475.6</v>
       </c>
       <c r="S4" t="n">
-        <v>478.4359363815904</v>
+        <v>45.17</v>
       </c>
       <c r="T4" t="n">
-        <v>45.8823878809339</v>
+        <v>487.89</v>
       </c>
       <c r="U4" t="n">
-        <v>480.1833546355676</v>
+        <v>59.29</v>
       </c>
       <c r="V4" t="n">
-        <v>43.07364288738421</v>
+        <v>488.14</v>
       </c>
       <c r="W4" t="n">
-        <v>480.9036756322714</v>
+        <v>51.08</v>
       </c>
       <c r="X4" t="n">
-        <v>46.04709723152109</v>
+        <v>491.27</v>
       </c>
       <c r="Y4" t="n">
-        <v>481.8586131068683</v>
+        <v>46.55</v>
       </c>
       <c r="Z4" t="n">
-        <v>46.8958616839731</v>
+        <v>488.14</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.85</v>
+        <v>57.97</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.4915254237288136</v>
+        <v>488.22</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.3417721518987342</v>
+        <v>52.72</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.2525252525252525</v>
+        <v>488.6</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.1764705882352941</v>
+        <v>49.77</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.1654676258992806</v>
+        <v>491.95</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.1320754716981132</v>
+        <v>46.2</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.106145251396648</v>
+        <v>492.33</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.09547738693467336</v>
+        <v>45</v>
       </c>
       <c r="AJ4" t="n">
-        <v>458.225</v>
+        <v>-0.7894736842105263</v>
       </c>
       <c r="AK4" t="n">
-        <v>473.8</v>
+        <v>-0.2413793103448276</v>
       </c>
       <c r="AL4" t="n">
-        <v>474.0375</v>
+        <v>-0.2051282051282051</v>
       </c>
       <c r="AM4" t="n">
-        <v>475.22</v>
+        <v>-0.1224489795918367</v>
       </c>
       <c r="AN4" t="n">
-        <v>476.7833333333334</v>
+        <v>-0.1186440677966102</v>
       </c>
       <c r="AO4" t="n">
-        <v>476.2071428571429</v>
+        <v>-0.1014492753623188</v>
       </c>
       <c r="AP4" t="n">
-        <v>476.8</v>
+        <v>-0.0759493670886076</v>
       </c>
       <c r="AQ4" t="n">
-        <v>477.8</v>
+        <v>-0.07865168539325842</v>
       </c>
       <c r="AR4" t="n">
-        <v>478.075</v>
+        <v>-0.08080808080808081</v>
       </c>
       <c r="AS4" t="n">
-        <v>32.87893512570016</v>
+        <v>460.3</v>
       </c>
       <c r="AT4" t="n">
-        <v>40.79534287146022</v>
+        <v>486.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>43.68278944561576</v>
+        <v>484.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>43.97080394989385</v>
+        <v>487.74</v>
       </c>
       <c r="AW4" t="n">
-        <v>45.30786968679453</v>
+        <v>487.5333333333334</v>
       </c>
       <c r="AX4" t="n">
-        <v>46.29000145489172</v>
+        <v>487.6428571428572</v>
       </c>
       <c r="AY4" t="n">
-        <v>46.29036076765875</v>
+        <v>487.85625</v>
       </c>
       <c r="AZ4" t="n">
-        <v>46.2810736454739</v>
+        <v>487.6722222222222</v>
       </c>
       <c r="BA4" t="n">
-        <v>46.31273447983827</v>
+        <v>487.62</v>
       </c>
       <c r="BB4" t="n">
-        <v>356</v>
+        <v>42.0417649486793</v>
       </c>
       <c r="BC4" t="n">
-        <v>356</v>
+        <v>57.13253597265455</v>
       </c>
       <c r="BD4" t="n">
-        <v>356</v>
+        <v>57.89594113579984</v>
       </c>
       <c r="BE4" t="n">
-        <v>356</v>
+        <v>57.22492813451144</v>
       </c>
       <c r="BF4" t="n">
-        <v>356</v>
+        <v>56.34195200341887</v>
       </c>
       <c r="BG4" t="n">
-        <v>356</v>
+        <v>56.21846054564683</v>
       </c>
       <c r="BH4" t="n">
-        <v>356</v>
+        <v>55.57167071393032</v>
       </c>
       <c r="BI4" t="n">
-        <v>356</v>
+        <v>54.20422600945383</v>
       </c>
       <c r="BJ4" t="n">
-        <v>356</v>
+        <v>52.74983981018331</v>
       </c>
       <c r="BK4" t="n">
-        <v>519</v>
+        <v>354</v>
       </c>
       <c r="BL4" t="n">
-        <v>549</v>
+        <v>354</v>
       </c>
       <c r="BM4" t="n">
-        <v>549</v>
+        <v>354</v>
       </c>
       <c r="BN4" t="n">
-        <v>549</v>
+        <v>354</v>
       </c>
       <c r="BO4" t="n">
-        <v>549</v>
+        <v>354</v>
       </c>
       <c r="BP4" t="n">
-        <v>549</v>
+        <v>354</v>
       </c>
       <c r="BQ4" t="n">
-        <v>549</v>
+        <v>354</v>
       </c>
       <c r="BR4" t="n">
-        <v>549</v>
+        <v>354</v>
       </c>
       <c r="BS4" t="n">
-        <v>549</v>
+        <v>354</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.2</v>
+        <v>544</v>
       </c>
       <c r="BU4" t="n">
+        <v>573</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>573</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>573</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>573</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>573</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>573</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>573</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>573</v>
+      </c>
+      <c r="CC4" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="BV4" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>0.7857142857142857</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>0.7647058823529411</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="CB4" t="n">
-        <v>0.90625</v>
+      <c r="CD4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>492.33</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S05_G2_478_38_ABS1</t>
+          <t>S04_G2_478_39_ABS1</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>478</v>
       </c>
       <c r="C5" t="n">
-        <v>38</v>
+        <v>57.82060785767235</v>
       </c>
       <c r="D5" t="n">
-        <v>56.33802816901409</v>
+        <v>39</v>
       </c>
       <c r="E5" t="n">
         <v>478</v>
@@ -1590,244 +1744,277 @@
         <v>200</v>
       </c>
       <c r="G5" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="H5" t="inlineStr">
+        <v>74.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>458.85242946945</v>
-      </c>
-      <c r="J5" t="n">
-        <v>18.53736245172664</v>
-      </c>
-      <c r="K5" t="n">
-        <v>460.2584715230199</v>
-      </c>
-      <c r="L5" t="n">
-        <v>18.7946455292422</v>
-      </c>
-      <c r="M5" t="n">
-        <v>463.6009430829498</v>
-      </c>
-      <c r="N5" t="n">
-        <v>21.18354293594249</v>
-      </c>
-      <c r="O5" t="n">
-        <v>463.406469693429</v>
-      </c>
-      <c r="P5" t="n">
-        <v>27.25300157982386</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>464.1642143801174</v>
-      </c>
       <c r="R5" t="n">
-        <v>29.17612865665606</v>
+        <v>461.7</v>
       </c>
       <c r="S5" t="n">
-        <v>471.0426902102134</v>
+        <v>53.8</v>
       </c>
       <c r="T5" t="n">
-        <v>44.50897620871533</v>
+        <v>464.09</v>
       </c>
       <c r="U5" t="n">
-        <v>469.7950073534875</v>
+        <v>39.66</v>
       </c>
       <c r="V5" t="n">
-        <v>41.22223473731609</v>
+        <v>463.34</v>
       </c>
       <c r="W5" t="n">
-        <v>471.3439017730959</v>
+        <v>42.05</v>
       </c>
       <c r="X5" t="n">
-        <v>42.02570620113215</v>
+        <v>464.73</v>
       </c>
       <c r="Y5" t="n">
-        <v>471.9001674093378</v>
+        <v>39.42</v>
       </c>
       <c r="Z5" t="n">
-        <v>40.07926511064863</v>
+        <v>470.57</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.9</v>
+        <v>41.25</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.9333333333333333</v>
+        <v>471</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.95</v>
+        <v>39.67</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.9399999999999999</v>
+        <v>469.42</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.8833333333333333</v>
+        <v>42.92</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.6142857142857143</v>
+        <v>469.58</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.4875</v>
+        <v>40.44</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.4222222222222222</v>
+        <v>471.09</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.3768844221105528</v>
+        <v>38.57</v>
       </c>
       <c r="AJ5" t="n">
-        <v>460.625</v>
+        <v>-0.2307692307692308</v>
       </c>
       <c r="AK5" t="n">
-        <v>459.5833333333333</v>
+        <v>-0.3448275862068966</v>
       </c>
       <c r="AL5" t="n">
-        <v>460.5</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="AM5" t="n">
-        <v>462.77</v>
+        <v>-0.3877551020408163</v>
       </c>
       <c r="AN5" t="n">
-        <v>460.7916666666667</v>
+        <v>-0.396551724137931</v>
       </c>
       <c r="AO5" t="n">
-        <v>468.5</v>
+        <v>-0.4117647058823529</v>
       </c>
       <c r="AP5" t="n">
-        <v>471.575</v>
+        <v>-0.3461538461538461</v>
       </c>
       <c r="AQ5" t="n">
-        <v>471.9555555555556</v>
+        <v>-0.3295454545454545</v>
       </c>
       <c r="AR5" t="n">
-        <v>472.34</v>
+        <v>-0.3163265306122449</v>
       </c>
       <c r="AS5" t="n">
-        <v>27.56509341540493</v>
+        <v>470.35</v>
       </c>
       <c r="AT5" t="n">
-        <v>27.13318488902883</v>
+        <v>466.4666666666666</v>
       </c>
       <c r="AU5" t="n">
-        <v>26.07489213784019</v>
+        <v>467.1625</v>
       </c>
       <c r="AV5" t="n">
-        <v>26.40676239147844</v>
+        <v>466.06</v>
       </c>
       <c r="AW5" t="n">
-        <v>28.62163978336826</v>
+        <v>466.6416666666667</v>
       </c>
       <c r="AX5" t="n">
-        <v>32.70113584746385</v>
+        <v>466.5714285714286</v>
       </c>
       <c r="AY5" t="n">
-        <v>36.61481086937361</v>
+        <v>468.68125</v>
       </c>
       <c r="AZ5" t="n">
-        <v>38.32910443662336</v>
+        <v>468.0333333333334</v>
       </c>
       <c r="BA5" t="n">
-        <v>39.02363898972006</v>
+        <v>468.11</v>
       </c>
       <c r="BB5" t="n">
-        <v>364</v>
+        <v>63.10489283724361</v>
       </c>
       <c r="BC5" t="n">
-        <v>364</v>
+        <v>56.80213219785171</v>
       </c>
       <c r="BD5" t="n">
-        <v>364</v>
+        <v>53.09318311939867</v>
       </c>
       <c r="BE5" t="n">
-        <v>364</v>
+        <v>50.21988052554486</v>
       </c>
       <c r="BF5" t="n">
-        <v>364</v>
+        <v>48.39435157008397</v>
       </c>
       <c r="BG5" t="n">
-        <v>364</v>
+        <v>46.92108007177627</v>
       </c>
       <c r="BH5" t="n">
-        <v>364</v>
+        <v>46.42525873312393</v>
       </c>
       <c r="BI5" t="n">
-        <v>364</v>
+        <v>45.85822354460176</v>
       </c>
       <c r="BJ5" t="n">
-        <v>364</v>
+        <v>45.04784012580404</v>
       </c>
       <c r="BK5" t="n">
-        <v>531</v>
+        <v>374</v>
       </c>
       <c r="BL5" t="n">
-        <v>531</v>
+        <v>374</v>
       </c>
       <c r="BM5" t="n">
-        <v>531</v>
+        <v>374</v>
       </c>
       <c r="BN5" t="n">
-        <v>531</v>
+        <v>374</v>
       </c>
       <c r="BO5" t="n">
-        <v>531</v>
+        <v>374</v>
       </c>
       <c r="BP5" t="n">
-        <v>537</v>
+        <v>374</v>
       </c>
       <c r="BQ5" t="n">
-        <v>539</v>
+        <v>374</v>
       </c>
       <c r="BR5" t="n">
-        <v>539</v>
+        <v>374</v>
       </c>
       <c r="BS5" t="n">
-        <v>539</v>
+        <v>374</v>
       </c>
       <c r="BT5" t="n">
-        <v>1</v>
+        <v>651</v>
       </c>
       <c r="BU5" t="n">
+        <v>651</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>651</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>651</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>651</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>651</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>651</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>651</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>651</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD5" t="n">
         <v>0.7272727272727273</v>
       </c>
-      <c r="BV5" t="n">
-        <v>0.7692307692307693</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>0.9375</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>0.5294117647058824</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="CB5" t="n">
-        <v>0.8333333333333334</v>
+      <c r="CE5" t="n">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0.8275862068965517</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0.975609756097561</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>471.09</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>38.57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S04_G2_478_39_ABS1</t>
+          <t>S05_G2_478_38_ABS1</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>478</v>
       </c>
       <c r="C6" t="n">
-        <v>39</v>
+        <v>56.33802816901409</v>
       </c>
       <c r="D6" t="n">
-        <v>57.82060785767235</v>
+        <v>38</v>
       </c>
       <c r="E6" t="n">
         <v>478</v>
@@ -1836,228 +2023,261 @@
         <v>200</v>
       </c>
       <c r="G6" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="H6" t="inlineStr">
+        <v>65</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>461.6972326095831</v>
-      </c>
-      <c r="J6" t="n">
-        <v>53.79698520913816</v>
-      </c>
-      <c r="K6" t="n">
-        <v>464.0909138332449</v>
-      </c>
-      <c r="L6" t="n">
-        <v>39.663290485956</v>
-      </c>
-      <c r="M6" t="n">
-        <v>463.3408941827681</v>
-      </c>
-      <c r="N6" t="n">
-        <v>42.04506241028271</v>
-      </c>
-      <c r="O6" t="n">
-        <v>464.732330119944</v>
-      </c>
-      <c r="P6" t="n">
-        <v>39.4201601139743</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>470.5732094216218</v>
-      </c>
       <c r="R6" t="n">
-        <v>41.2472959728378</v>
+        <v>458.85</v>
       </c>
       <c r="S6" t="n">
-        <v>471.0030133217718</v>
+        <v>18.54</v>
       </c>
       <c r="T6" t="n">
-        <v>39.66681239711656</v>
+        <v>460.26</v>
       </c>
       <c r="U6" t="n">
-        <v>469.4229664537781</v>
+        <v>18.79</v>
       </c>
       <c r="V6" t="n">
-        <v>42.91555936228446</v>
+        <v>463.6</v>
       </c>
       <c r="W6" t="n">
-        <v>469.5764046168972</v>
+        <v>21.18</v>
       </c>
       <c r="X6" t="n">
-        <v>40.43950680644944</v>
+        <v>463.41</v>
       </c>
       <c r="Y6" t="n">
-        <v>471.0936266015262</v>
+        <v>27.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>38.56535681968331</v>
+        <v>464.16</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.2307692307692308</v>
+        <v>29.18</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.3448275862068966</v>
+        <v>471.04</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.3333333333333333</v>
+        <v>44.51</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.3877551020408163</v>
+        <v>469.8</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.396551724137931</v>
+        <v>41.22</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.4117647058823529</v>
+        <v>471.34</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.3461538461538461</v>
+        <v>42.03</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.3295454545454545</v>
+        <v>471.9</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.3163265306122449</v>
+        <v>40.08</v>
       </c>
       <c r="AJ6" t="n">
-        <v>470.35</v>
+        <v>-0.9</v>
       </c>
       <c r="AK6" t="n">
-        <v>466.4666666666666</v>
+        <v>-0.9333333333333333</v>
       </c>
       <c r="AL6" t="n">
-        <v>467.1625</v>
+        <v>-0.95</v>
       </c>
       <c r="AM6" t="n">
-        <v>466.06</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AN6" t="n">
-        <v>466.6416666666667</v>
+        <v>-0.8833333333333333</v>
       </c>
       <c r="AO6" t="n">
-        <v>466.5714285714286</v>
+        <v>-0.6142857142857143</v>
       </c>
       <c r="AP6" t="n">
-        <v>468.68125</v>
+        <v>-0.4875</v>
       </c>
       <c r="AQ6" t="n">
-        <v>468.0333333333334</v>
+        <v>-0.4222222222222222</v>
       </c>
       <c r="AR6" t="n">
-        <v>468.11</v>
+        <v>-0.3768844221105528</v>
       </c>
       <c r="AS6" t="n">
-        <v>63.10489283724361</v>
+        <v>460.625</v>
       </c>
       <c r="AT6" t="n">
-        <v>56.80213219785171</v>
+        <v>459.5833333333333</v>
       </c>
       <c r="AU6" t="n">
-        <v>53.09318311939867</v>
+        <v>460.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>50.21988052554486</v>
+        <v>462.77</v>
       </c>
       <c r="AW6" t="n">
-        <v>48.39435157008397</v>
+        <v>460.7916666666667</v>
       </c>
       <c r="AX6" t="n">
-        <v>46.92108007177627</v>
+        <v>468.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>46.42525873312393</v>
+        <v>471.575</v>
       </c>
       <c r="AZ6" t="n">
-        <v>45.85822354460176</v>
+        <v>471.9555555555556</v>
       </c>
       <c r="BA6" t="n">
-        <v>45.04784012580404</v>
+        <v>472.34</v>
       </c>
       <c r="BB6" t="n">
-        <v>374</v>
+        <v>27.56509341540493</v>
       </c>
       <c r="BC6" t="n">
-        <v>374</v>
+        <v>27.13318488902883</v>
       </c>
       <c r="BD6" t="n">
-        <v>374</v>
+        <v>26.07489213784019</v>
       </c>
       <c r="BE6" t="n">
-        <v>374</v>
+        <v>26.40676239147844</v>
       </c>
       <c r="BF6" t="n">
-        <v>374</v>
+        <v>28.62163978336826</v>
       </c>
       <c r="BG6" t="n">
-        <v>374</v>
+        <v>32.70113584746385</v>
       </c>
       <c r="BH6" t="n">
-        <v>374</v>
+        <v>36.61481086937361</v>
       </c>
       <c r="BI6" t="n">
-        <v>374</v>
+        <v>38.32910443662336</v>
       </c>
       <c r="BJ6" t="n">
-        <v>374</v>
+        <v>39.02363898972006</v>
       </c>
       <c r="BK6" t="n">
-        <v>651</v>
+        <v>364</v>
       </c>
       <c r="BL6" t="n">
-        <v>651</v>
+        <v>364</v>
       </c>
       <c r="BM6" t="n">
-        <v>651</v>
+        <v>364</v>
       </c>
       <c r="BN6" t="n">
-        <v>651</v>
+        <v>364</v>
       </c>
       <c r="BO6" t="n">
-        <v>651</v>
+        <v>364</v>
       </c>
       <c r="BP6" t="n">
-        <v>651</v>
+        <v>364</v>
       </c>
       <c r="BQ6" t="n">
-        <v>651</v>
+        <v>364</v>
       </c>
       <c r="BR6" t="n">
-        <v>651</v>
+        <v>364</v>
       </c>
       <c r="BS6" t="n">
-        <v>651</v>
+        <v>364</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>531</v>
       </c>
       <c r="BU6" t="n">
+        <v>531</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>531</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>531</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>531</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>537</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>539</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>539</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>539</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD6" t="n">
         <v>0.7272727272727273</v>
       </c>
-      <c r="BV6" t="n">
-        <v>0.7647058823529411</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>0.9166666666666666</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>0.8275862068965517</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>0.9333333333333333</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>0.9230769230769231</v>
-      </c>
-      <c r="CB6" t="n">
-        <v>0.975609756097561</v>
+      <c r="CE6" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0.5294117647058824</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>471.9</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>40.08</v>
       </c>
     </row>
     <row r="7">
@@ -2070,10 +2290,10 @@
         <v>481</v>
       </c>
       <c r="C7" t="n">
+        <v>62.26834692364714</v>
+      </c>
+      <c r="D7" t="n">
         <v>42</v>
-      </c>
-      <c r="D7" t="n">
-        <v>62.26834692364714</v>
       </c>
       <c r="E7" t="n">
         <v>481</v>
@@ -2082,228 +2302,261 @@
         <v>200</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H7" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>497.2784689166232</v>
-      </c>
-      <c r="J7" t="n">
-        <v>57.63495385185927</v>
-      </c>
-      <c r="K7" t="n">
-        <v>499.0960737777269</v>
-      </c>
-      <c r="L7" t="n">
-        <v>53.72309394788586</v>
-      </c>
-      <c r="M7" t="n">
-        <v>491.4083370324508</v>
-      </c>
-      <c r="N7" t="n">
-        <v>57.76275125468725</v>
-      </c>
-      <c r="O7" t="n">
-        <v>493.6362770523509</v>
-      </c>
-      <c r="P7" t="n">
-        <v>59.09066517032233</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>487.6260411307591</v>
-      </c>
       <c r="R7" t="n">
-        <v>54.26050627994779</v>
+        <v>497.28</v>
       </c>
       <c r="S7" t="n">
-        <v>484.9490270980573</v>
+        <v>57.63</v>
       </c>
       <c r="T7" t="n">
-        <v>58.56375253891176</v>
+        <v>499.1</v>
       </c>
       <c r="U7" t="n">
-        <v>485.1301963849129</v>
+        <v>53.72</v>
       </c>
       <c r="V7" t="n">
-        <v>58.04583259093663</v>
+        <v>491.41</v>
       </c>
       <c r="W7" t="n">
-        <v>490.2499264318551</v>
+        <v>57.76</v>
       </c>
       <c r="X7" t="n">
-        <v>57.06720533184037</v>
+        <v>493.64</v>
       </c>
       <c r="Y7" t="n">
-        <v>493.5330088172444</v>
+        <v>59.09</v>
       </c>
       <c r="Z7" t="n">
-        <v>55.43962060924405</v>
+        <v>487.63</v>
       </c>
       <c r="AA7" t="n">
+        <v>54.26</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>484.95</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>58.56</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>485.13</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>58.05</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>490.25</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>57.07</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>493.53</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>55.44</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>0</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AK7" t="n">
         <v>0.06666666666666667</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AL7" t="n">
         <v>0.025</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AM7" t="n">
         <v>0.02</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AN7" t="n">
         <v>0.03333333333333333</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AO7" t="n">
         <v>0.02857142857142857</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AP7" t="n">
         <v>0.0125</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AQ7" t="n">
         <v>0.02222222222222222</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AR7" t="n">
         <v>0.03</v>
       </c>
-      <c r="AJ7" t="n">
+      <c r="AS7" t="n">
         <v>504.3</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="AT7" t="n">
         <v>506.65</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AU7" t="n">
         <v>501.025</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="AV7" t="n">
         <v>498.83</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AW7" t="n">
         <v>497.7166666666666</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="AX7" t="n">
         <v>495.7071428571429</v>
       </c>
-      <c r="AP7" t="n">
+      <c r="AY7" t="n">
         <v>493.0875</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AZ7" t="n">
         <v>492.8555555555556</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="BA7" t="n">
         <v>493.165</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="BB7" t="n">
         <v>59.50386542065986</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="BC7" t="n">
         <v>60.90479592500633</v>
       </c>
-      <c r="AU7" t="n">
+      <c r="BD7" t="n">
         <v>58.61569222486415</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="BE7" t="n">
         <v>59.01627826286575</v>
       </c>
-      <c r="AW7" t="n">
+      <c r="BF7" t="n">
         <v>59.02191448003774</v>
       </c>
-      <c r="AX7" t="n">
+      <c r="BG7" t="n">
         <v>58.17320154118235</v>
       </c>
-      <c r="AY7" t="n">
+      <c r="BH7" t="n">
         <v>58.7458921436214</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BI7" t="n">
         <v>58.27951061929648</v>
       </c>
-      <c r="BA7" t="n">
+      <c r="BJ7" t="n">
         <v>57.9071478748522</v>
       </c>
-      <c r="BB7" t="n">
+      <c r="BK7" t="n">
         <v>410</v>
       </c>
-      <c r="BC7" t="n">
+      <c r="BL7" t="n">
         <v>410</v>
       </c>
-      <c r="BD7" t="n">
+      <c r="BM7" t="n">
         <v>410</v>
       </c>
-      <c r="BE7" t="n">
+      <c r="BN7" t="n">
         <v>410</v>
       </c>
-      <c r="BF7" t="n">
+      <c r="BO7" t="n">
         <v>410</v>
       </c>
-      <c r="BG7" t="n">
+      <c r="BP7" t="n">
         <v>410</v>
       </c>
-      <c r="BH7" t="n">
+      <c r="BQ7" t="n">
         <v>410</v>
       </c>
-      <c r="BI7" t="n">
+      <c r="BR7" t="n">
         <v>410</v>
       </c>
-      <c r="BJ7" t="n">
+      <c r="BS7" t="n">
         <v>410</v>
       </c>
-      <c r="BK7" t="n">
+      <c r="BT7" t="n">
         <v>638</v>
       </c>
-      <c r="BL7" t="n">
+      <c r="BU7" t="n">
         <v>638</v>
       </c>
-      <c r="BM7" t="n">
+      <c r="BV7" t="n">
         <v>638</v>
       </c>
-      <c r="BN7" t="n">
+      <c r="BW7" t="n">
         <v>638</v>
       </c>
-      <c r="BO7" t="n">
+      <c r="BX7" t="n">
         <v>638</v>
       </c>
-      <c r="BP7" t="n">
+      <c r="BY7" t="n">
         <v>638</v>
       </c>
-      <c r="BQ7" t="n">
+      <c r="BZ7" t="n">
         <v>638</v>
       </c>
-      <c r="BR7" t="n">
+      <c r="CA7" t="n">
         <v>638</v>
       </c>
-      <c r="BS7" t="n">
+      <c r="CB7" t="n">
         <v>638</v>
       </c>
-      <c r="BT7" t="n">
+      <c r="CC7" t="n">
         <v>0.8</v>
       </c>
-      <c r="BU7" t="n">
+      <c r="CD7" t="n">
         <v>0.6</v>
       </c>
-      <c r="BV7" t="n">
+      <c r="CE7" t="n">
         <v>0.6</v>
       </c>
-      <c r="BW7" t="n">
+      <c r="CF7" t="n">
         <v>1</v>
       </c>
-      <c r="BX7" t="n">
+      <c r="CG7" t="n">
         <v>1</v>
       </c>
-      <c r="BY7" t="n">
+      <c r="CH7" t="n">
         <v>0.8</v>
       </c>
-      <c r="BZ7" t="n">
+      <c r="CI7" t="n">
         <v>0.8260869565217391</v>
       </c>
-      <c r="CA7" t="n">
+      <c r="CJ7" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="CB7" t="n">
+      <c r="CK7" t="n">
         <v>0.9655172413793104</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>493.53</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>55.44</v>
       </c>
     </row>
     <row r="8">
@@ -2316,10 +2569,10 @@
         <v>478</v>
       </c>
       <c r="C8" t="n">
+        <v>59.30318754633062</v>
+      </c>
+      <c r="D8" t="n">
         <v>40</v>
-      </c>
-      <c r="D8" t="n">
-        <v>59.30318754633062</v>
       </c>
       <c r="E8" t="n">
         <v>478</v>
@@ -2328,228 +2581,261 @@
         <v>200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="H8" t="inlineStr">
+        <v>72</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>470.4803136450525</v>
-      </c>
-      <c r="J8" t="n">
-        <v>26.95466043885906</v>
-      </c>
-      <c r="K8" t="n">
-        <v>468.043605708625</v>
-      </c>
-      <c r="L8" t="n">
-        <v>38.33991464200285</v>
-      </c>
-      <c r="M8" t="n">
-        <v>469.1760773333535</v>
-      </c>
-      <c r="N8" t="n">
-        <v>35.59832536682514</v>
-      </c>
-      <c r="O8" t="n">
-        <v>468.5244555416731</v>
-      </c>
-      <c r="P8" t="n">
-        <v>35.38682175812583</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>467.9377279899182</v>
-      </c>
       <c r="R8" t="n">
-        <v>34.37203779719248</v>
+        <v>470.48</v>
       </c>
       <c r="S8" t="n">
-        <v>468.796116488142</v>
+        <v>26.95</v>
       </c>
       <c r="T8" t="n">
-        <v>35.10475060665563</v>
+        <v>468.04</v>
       </c>
       <c r="U8" t="n">
-        <v>471.6033687753209</v>
+        <v>38.34</v>
       </c>
       <c r="V8" t="n">
-        <v>40.19554862951311</v>
+        <v>469.18</v>
       </c>
       <c r="W8" t="n">
-        <v>471.2008675995915</v>
+        <v>35.6</v>
       </c>
       <c r="X8" t="n">
-        <v>40.46846431240266</v>
+        <v>468.52</v>
       </c>
       <c r="Y8" t="n">
-        <v>470.5815806080124</v>
+        <v>35.39</v>
       </c>
       <c r="Z8" t="n">
-        <v>41.56480900159211</v>
+        <v>467.94</v>
       </c>
       <c r="AA8" t="n">
+        <v>34.37</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>468.8</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>471.6</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>471.2</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>40.47</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>470.58</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>41.56</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>-0.6410256410256411</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AK8" t="n">
         <v>-0.5932203389830508</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AL8" t="n">
         <v>-0.3924050632911392</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AM8" t="n">
         <v>-0.3877551020408163</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AN8" t="n">
         <v>-0.3559322033898305</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AO8" t="n">
         <v>-0.3478260869565217</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AP8" t="n">
         <v>-0.2784810126582278</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AQ8" t="n">
         <v>-0.2584269662921349</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AR8" t="n">
         <v>-0.2323232323232323</v>
       </c>
-      <c r="AJ8" t="n">
+      <c r="AS8" t="n">
         <v>469.1</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AT8" t="n">
         <v>465.2833333333334</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AU8" t="n">
         <v>468.925</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AV8" t="n">
         <v>468.52</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AW8" t="n">
         <v>469.0166666666667</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="AX8" t="n">
         <v>469.6</v>
       </c>
-      <c r="AP8" t="n">
+      <c r="AY8" t="n">
         <v>471.26875</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AZ8" t="n">
         <v>470.8277777777778</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="BA8" t="n">
         <v>471.145</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="BB8" t="n">
         <v>28.79565939512412</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="BC8" t="n">
         <v>32.97276232825444</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="BD8" t="n">
         <v>37.42785560247875</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="BE8" t="n">
         <v>37.27102896352608</v>
       </c>
-      <c r="AW8" t="n">
+      <c r="BF8" t="n">
         <v>36.91792322917902</v>
       </c>
-      <c r="AX8" t="n">
+      <c r="BG8" t="n">
         <v>36.33667961873079</v>
       </c>
-      <c r="AY8" t="n">
+      <c r="BH8" t="n">
         <v>37.75922434899186</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BI8" t="n">
         <v>38.71689705133859</v>
       </c>
-      <c r="BA8" t="n">
+      <c r="BJ8" t="n">
         <v>39.25906232960741</v>
       </c>
-      <c r="BB8" t="n">
+      <c r="BK8" t="n">
         <v>370</v>
       </c>
-      <c r="BC8" t="n">
+      <c r="BL8" t="n">
         <v>370</v>
       </c>
-      <c r="BD8" t="n">
+      <c r="BM8" t="n">
         <v>370</v>
       </c>
-      <c r="BE8" t="n">
+      <c r="BN8" t="n">
         <v>370</v>
       </c>
-      <c r="BF8" t="n">
+      <c r="BO8" t="n">
         <v>370</v>
       </c>
-      <c r="BG8" t="n">
+      <c r="BP8" t="n">
         <v>370</v>
       </c>
-      <c r="BH8" t="n">
+      <c r="BQ8" t="n">
         <v>370</v>
       </c>
-      <c r="BI8" t="n">
+      <c r="BR8" t="n">
         <v>370</v>
       </c>
-      <c r="BJ8" t="n">
+      <c r="BS8" t="n">
         <v>370</v>
       </c>
-      <c r="BK8" t="n">
+      <c r="BT8" t="n">
         <v>513</v>
       </c>
-      <c r="BL8" t="n">
+      <c r="BU8" t="n">
         <v>531</v>
       </c>
-      <c r="BM8" t="n">
+      <c r="BV8" t="n">
         <v>531</v>
       </c>
-      <c r="BN8" t="n">
+      <c r="BW8" t="n">
         <v>531</v>
       </c>
-      <c r="BO8" t="n">
+      <c r="BX8" t="n">
         <v>531</v>
       </c>
-      <c r="BP8" t="n">
+      <c r="BY8" t="n">
         <v>531</v>
       </c>
-      <c r="BQ8" t="n">
+      <c r="BZ8" t="n">
         <v>531</v>
       </c>
-      <c r="BR8" t="n">
+      <c r="CA8" t="n">
         <v>531</v>
       </c>
-      <c r="BS8" t="n">
+      <c r="CB8" t="n">
         <v>531</v>
       </c>
-      <c r="BT8" t="n">
+      <c r="CC8" t="n">
         <v>1</v>
       </c>
-      <c r="BU8" t="n">
+      <c r="CD8" t="n">
         <v>1</v>
       </c>
-      <c r="BV8" t="n">
+      <c r="CE8" t="n">
         <v>1</v>
       </c>
-      <c r="BW8" t="n">
+      <c r="CF8" t="n">
         <v>0.9333333333333333</v>
       </c>
-      <c r="BX8" t="n">
+      <c r="CG8" t="n">
         <v>0.8</v>
       </c>
-      <c r="BY8" t="n">
+      <c r="CH8" t="n">
         <v>0.7727272727272727</v>
       </c>
-      <c r="BZ8" t="n">
+      <c r="CI8" t="n">
         <v>0.8260869565217391</v>
       </c>
-      <c r="CA8" t="n">
+      <c r="CJ8" t="n">
         <v>0.875</v>
       </c>
-      <c r="CB8" t="n">
+      <c r="CK8" t="n">
         <v>0.8888888888888888</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>470.58</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>41.56</v>
       </c>
     </row>
     <row r="9">
@@ -2562,10 +2848,10 @@
         <v>482</v>
       </c>
       <c r="C9" t="n">
+        <v>62.26834692364714</v>
+      </c>
+      <c r="D9" t="n">
         <v>42</v>
-      </c>
-      <c r="D9" t="n">
-        <v>62.26834692364714</v>
       </c>
       <c r="E9" t="n">
         <v>482</v>
@@ -2574,228 +2860,261 @@
         <v>200</v>
       </c>
       <c r="G9" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H9" t="inlineStr">
+        <v>69.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>470.3209610370322</v>
-      </c>
-      <c r="J9" t="n">
-        <v>45.85812352601005</v>
-      </c>
-      <c r="K9" t="n">
-        <v>470.1351474390623</v>
-      </c>
-      <c r="L9" t="n">
-        <v>38.2752041389997</v>
-      </c>
-      <c r="M9" t="n">
-        <v>467.3902299563375</v>
-      </c>
-      <c r="N9" t="n">
-        <v>31.86428492633699</v>
-      </c>
-      <c r="O9" t="n">
-        <v>461.9195336385889</v>
-      </c>
-      <c r="P9" t="n">
-        <v>36.84149011206169</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>461.8920962023446</v>
-      </c>
       <c r="R9" t="n">
-        <v>39.68053070825589</v>
+        <v>470.32</v>
       </c>
       <c r="S9" t="n">
-        <v>465.0611804661007</v>
+        <v>45.86</v>
       </c>
       <c r="T9" t="n">
-        <v>44.71912959048319</v>
+        <v>470.14</v>
       </c>
       <c r="U9" t="n">
-        <v>467.3234092770369</v>
+        <v>38.28</v>
       </c>
       <c r="V9" t="n">
-        <v>48.56342723971112</v>
+        <v>467.39</v>
       </c>
       <c r="W9" t="n">
-        <v>468.7536246637865</v>
+        <v>31.86</v>
       </c>
       <c r="X9" t="n">
-        <v>52.29900187727281</v>
+        <v>461.92</v>
       </c>
       <c r="Y9" t="n">
-        <v>470.2573295105023</v>
+        <v>36.84</v>
       </c>
       <c r="Z9" t="n">
-        <v>53.08498229832625</v>
+        <v>461.89</v>
       </c>
       <c r="AA9" t="n">
+        <v>39.68</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>465.06</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>44.72</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>467.32</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>48.56</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>468.75</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>470.26</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>53.08</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AK9" t="n">
         <v>-0.2333333333333333</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AL9" t="n">
         <v>-0.3164556962025317</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AM9" t="n">
         <v>-0.4343434343434344</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AN9" t="n">
         <v>-0.4745762711864407</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AO9" t="n">
         <v>-0.4306569343065693</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AP9" t="n">
         <v>-0.3630573248407643</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AQ9" t="n">
         <v>-0.2994350282485876</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AR9" t="n">
         <v>-0.2487309644670051</v>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AS9" t="n">
         <v>469.2</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AT9" t="n">
         <v>469.6166666666667</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AU9" t="n">
         <v>470.725</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AV9" t="n">
         <v>467.25</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AW9" t="n">
         <v>465.075</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="AX9" t="n">
         <v>465.0857142857143</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="AY9" t="n">
         <v>466.0375</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AZ9" t="n">
         <v>467.3777777777778</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="BA9" t="n">
         <v>468.885</v>
       </c>
-      <c r="AS9" t="n">
+      <c r="BB9" t="n">
         <v>52.22413235277346</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="BC9" t="n">
         <v>49.19217135096012</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="BD9" t="n">
         <v>45.23438266407535</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="BE9" t="n">
         <v>43.03797741530148</v>
       </c>
-      <c r="AW9" t="n">
+      <c r="BF9" t="n">
         <v>42.94806214099382</v>
       </c>
-      <c r="AX9" t="n">
+      <c r="BG9" t="n">
         <v>43.30003063580006</v>
       </c>
-      <c r="AY9" t="n">
+      <c r="BH9" t="n">
         <v>44.23373818421862</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BI9" t="n">
         <v>46.18515340519861</v>
       </c>
-      <c r="BA9" t="n">
+      <c r="BJ9" t="n">
         <v>47.93080194405263</v>
       </c>
-      <c r="BB9" t="n">
+      <c r="BK9" t="n">
         <v>344</v>
       </c>
-      <c r="BC9" t="n">
+      <c r="BL9" t="n">
         <v>344</v>
       </c>
-      <c r="BD9" t="n">
+      <c r="BM9" t="n">
         <v>344</v>
       </c>
-      <c r="BE9" t="n">
+      <c r="BN9" t="n">
         <v>344</v>
       </c>
-      <c r="BF9" t="n">
+      <c r="BO9" t="n">
         <v>344</v>
       </c>
-      <c r="BG9" t="n">
+      <c r="BP9" t="n">
         <v>344</v>
       </c>
-      <c r="BH9" t="n">
+      <c r="BQ9" t="n">
         <v>344</v>
       </c>
-      <c r="BI9" t="n">
+      <c r="BR9" t="n">
         <v>344</v>
       </c>
-      <c r="BJ9" t="n">
+      <c r="BS9" t="n">
         <v>344</v>
       </c>
-      <c r="BK9" t="n">
+      <c r="BT9" t="n">
         <v>584</v>
       </c>
-      <c r="BL9" t="n">
+      <c r="BU9" t="n">
         <v>584</v>
       </c>
-      <c r="BM9" t="n">
+      <c r="BV9" t="n">
         <v>584</v>
       </c>
-      <c r="BN9" t="n">
+      <c r="BW9" t="n">
         <v>584</v>
       </c>
-      <c r="BO9" t="n">
+      <c r="BX9" t="n">
         <v>584</v>
       </c>
-      <c r="BP9" t="n">
+      <c r="BY9" t="n">
         <v>584</v>
       </c>
-      <c r="BQ9" t="n">
+      <c r="BZ9" t="n">
         <v>584</v>
       </c>
-      <c r="BR9" t="n">
+      <c r="CA9" t="n">
         <v>584</v>
       </c>
-      <c r="BS9" t="n">
+      <c r="CB9" t="n">
         <v>584</v>
       </c>
-      <c r="BT9" t="n">
+      <c r="CC9" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="BU9" t="n">
+      <c r="CD9" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="BV9" t="n">
+      <c r="CE9" t="n">
         <v>0.9090909090909091</v>
       </c>
-      <c r="BW9" t="n">
+      <c r="CF9" t="n">
         <v>1</v>
       </c>
-      <c r="BX9" t="n">
+      <c r="CG9" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="BY9" t="n">
+      <c r="CH9" t="n">
         <v>0.9523809523809523</v>
       </c>
-      <c r="BZ9" t="n">
+      <c r="CI9" t="n">
         <v>0.9230769230769231</v>
       </c>
-      <c r="CA9" t="n">
+      <c r="CJ9" t="n">
         <v>0.9285714285714286</v>
       </c>
-      <c r="CB9" t="n">
+      <c r="CK9" t="n">
         <v>0.8387096774193549</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>470.26</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>53.08</v>
       </c>
     </row>
     <row r="10">
@@ -2808,10 +3127,10 @@
         <v>480</v>
       </c>
       <c r="C10" t="n">
+        <v>60.78576723498888</v>
+      </c>
+      <c r="D10" t="n">
         <v>41</v>
-      </c>
-      <c r="D10" t="n">
-        <v>60.78576723498888</v>
       </c>
       <c r="E10" t="n">
         <v>480</v>
@@ -2820,1474 +3139,1672 @@
         <v>200</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H10" t="inlineStr">
+        <v>73.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>479.5837845756326</v>
-      </c>
-      <c r="J10" t="n">
-        <v>40.89975259965404</v>
-      </c>
-      <c r="K10" t="n">
-        <v>487.2330622965728</v>
-      </c>
-      <c r="L10" t="n">
-        <v>45.94497891317609</v>
-      </c>
-      <c r="M10" t="n">
-        <v>490.7010383460417</v>
-      </c>
-      <c r="N10" t="n">
-        <v>40.53685497670919</v>
-      </c>
-      <c r="O10" t="n">
-        <v>498.9276256637365</v>
-      </c>
-      <c r="P10" t="n">
-        <v>38.97207933110824</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>499.0227585577422</v>
-      </c>
       <c r="R10" t="n">
-        <v>36.39674519004218</v>
+        <v>479.58</v>
       </c>
       <c r="S10" t="n">
-        <v>494.1454628947209</v>
+        <v>40.9</v>
       </c>
       <c r="T10" t="n">
-        <v>38.35314258732858</v>
+        <v>487.23</v>
       </c>
       <c r="U10" t="n">
-        <v>493.2468824532168</v>
+        <v>45.94</v>
       </c>
       <c r="V10" t="n">
-        <v>41.91034569427759</v>
+        <v>490.7</v>
       </c>
       <c r="W10" t="n">
-        <v>493.8023300837971</v>
+        <v>40.54</v>
       </c>
       <c r="X10" t="n">
-        <v>42.8018546396093</v>
+        <v>498.93</v>
       </c>
       <c r="Y10" t="n">
-        <v>490.64464905847</v>
+        <v>38.97</v>
       </c>
       <c r="Z10" t="n">
-        <v>45.6811403202223</v>
+        <v>499.02</v>
       </c>
       <c r="AA10" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>494.15</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>38.35</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>493.25</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>41.91</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>493.8</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>490.64</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>-0.282051282051282</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AK10" t="n">
         <v>-0.1186440677966102</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AL10" t="n">
         <v>-0.0379746835443038</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AM10" t="n">
         <v>-0.0303030303030303</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AN10" t="n">
         <v>-0.05882352941176471</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AO10" t="n">
         <v>-0.03597122302158273</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AP10" t="n">
         <v>-0.03144654088050314</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AQ10" t="n">
         <v>-0.02793296089385475</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AR10" t="n">
         <v>-0.05527638190954774</v>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AS10" t="n">
         <v>485.925</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AT10" t="n">
         <v>487.85</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AU10" t="n">
         <v>490.375</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AV10" t="n">
         <v>491.05</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AW10" t="n">
         <v>491.4333333333333</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="AX10" t="n">
         <v>492.5357142857143</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="AY10" t="n">
         <v>493.025</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AZ10" t="n">
         <v>492.55</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="BA10" t="n">
         <v>490.78</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="BB10" t="n">
         <v>47.61217675133117</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="BC10" t="n">
         <v>49.06792061350606</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="BD10" t="n">
         <v>49.73840945386171</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="BE10" t="n">
         <v>47.75759101964838</v>
       </c>
-      <c r="AW10" t="n">
+      <c r="BF10" t="n">
         <v>46.08556052484215</v>
       </c>
-      <c r="AX10" t="n">
+      <c r="BG10" t="n">
         <v>44.21011692786517</v>
       </c>
-      <c r="AY10" t="n">
+      <c r="BH10" t="n">
         <v>43.69667464464545</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BI10" t="n">
         <v>43.89080832652272</v>
       </c>
-      <c r="BA10" t="n">
+      <c r="BJ10" t="n">
         <v>44.18270702435512</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="BK10" t="n">
         <v>407</v>
       </c>
-      <c r="BC10" t="n">
+      <c r="BL10" t="n">
         <v>407</v>
       </c>
-      <c r="BD10" t="n">
+      <c r="BM10" t="n">
         <v>407</v>
       </c>
-      <c r="BE10" t="n">
+      <c r="BN10" t="n">
         <v>407</v>
       </c>
-      <c r="BF10" t="n">
+      <c r="BO10" t="n">
         <v>407</v>
       </c>
-      <c r="BG10" t="n">
+      <c r="BP10" t="n">
         <v>407</v>
       </c>
-      <c r="BH10" t="n">
+      <c r="BQ10" t="n">
         <v>407</v>
       </c>
-      <c r="BI10" t="n">
+      <c r="BR10" t="n">
         <v>407</v>
       </c>
-      <c r="BJ10" t="n">
+      <c r="BS10" t="n">
         <v>407</v>
       </c>
-      <c r="BK10" t="n">
+      <c r="BT10" t="n">
         <v>646</v>
       </c>
-      <c r="BL10" t="n">
+      <c r="BU10" t="n">
         <v>646</v>
       </c>
-      <c r="BM10" t="n">
+      <c r="BV10" t="n">
         <v>646</v>
       </c>
-      <c r="BN10" t="n">
+      <c r="BW10" t="n">
         <v>646</v>
       </c>
-      <c r="BO10" t="n">
+      <c r="BX10" t="n">
         <v>646</v>
       </c>
-      <c r="BP10" t="n">
+      <c r="BY10" t="n">
         <v>646</v>
       </c>
-      <c r="BQ10" t="n">
+      <c r="BZ10" t="n">
         <v>646</v>
       </c>
-      <c r="BR10" t="n">
+      <c r="CA10" t="n">
         <v>646</v>
       </c>
-      <c r="BS10" t="n">
+      <c r="CB10" t="n">
         <v>646</v>
       </c>
-      <c r="BT10" t="n">
+      <c r="CC10" t="n">
         <v>0.625</v>
       </c>
-      <c r="BU10" t="n">
+      <c r="CD10" t="n">
         <v>0.8</v>
       </c>
-      <c r="BV10" t="n">
+      <c r="CE10" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="BW10" t="n">
+      <c r="CF10" t="n">
         <v>0.875</v>
       </c>
-      <c r="BX10" t="n">
+      <c r="CG10" t="n">
         <v>0.7</v>
       </c>
-      <c r="BY10" t="n">
+      <c r="CH10" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BZ10" t="n">
+      <c r="CI10" t="n">
         <v>0.7037037037037037</v>
       </c>
-      <c r="CA10" t="n">
+      <c r="CJ10" t="n">
         <v>0.6176470588235294</v>
       </c>
-      <c r="CB10" t="n">
+      <c r="CK10" t="n">
         <v>0.2222222222222222</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>490.64</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>45.68</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S11_G2_478_38_ABS1</t>
+          <t>S10_G2_480_38_ABS1</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C11" t="n">
+        <v>56.33802816901409</v>
+      </c>
+      <c r="D11" t="n">
         <v>38</v>
       </c>
-      <c r="D11" t="n">
-        <v>56.33802816901409</v>
-      </c>
       <c r="E11" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F11" t="n">
         <v>200</v>
       </c>
       <c r="G11" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="H11" t="inlineStr">
+        <v>74</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>500.4026993442827</v>
-      </c>
-      <c r="J11" t="n">
-        <v>23.79099803324097</v>
-      </c>
-      <c r="K11" t="n">
-        <v>498.9472647556948</v>
-      </c>
-      <c r="L11" t="n">
-        <v>39.0615333309873</v>
-      </c>
-      <c r="M11" t="n">
-        <v>495.8003130761377</v>
-      </c>
-      <c r="N11" t="n">
-        <v>33.5050692513919</v>
-      </c>
-      <c r="O11" t="n">
-        <v>499.6972759947477</v>
-      </c>
-      <c r="P11" t="n">
-        <v>35.43066589775683</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>495.7982443565222</v>
-      </c>
       <c r="R11" t="n">
-        <v>37.78255913385909</v>
+        <v>451.99</v>
       </c>
       <c r="S11" t="n">
-        <v>492.1531716674568</v>
+        <v>47.33</v>
       </c>
       <c r="T11" t="n">
-        <v>38.24300925981485</v>
+        <v>457.83</v>
       </c>
       <c r="U11" t="n">
-        <v>489.6882256241369</v>
+        <v>45.68</v>
       </c>
       <c r="V11" t="n">
-        <v>37.78572726347879</v>
+        <v>461.13</v>
       </c>
       <c r="W11" t="n">
-        <v>489.8472266776384</v>
+        <v>49.55</v>
       </c>
       <c r="X11" t="n">
-        <v>38.07169553680157</v>
+        <v>468.88</v>
       </c>
       <c r="Y11" t="n">
-        <v>488.1436665745974</v>
+        <v>47.54</v>
       </c>
       <c r="Z11" t="n">
-        <v>36.62927712398613</v>
+        <v>470.44</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.2105263157894737</v>
+        <v>45.81</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.06896551724137931</v>
+        <v>469.75</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>43.71</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.06122448979591837</v>
+        <v>465.17</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.03389830508474576</v>
+        <v>40.76</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.01449275362318841</v>
+        <v>468.3</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.01265822784810127</v>
+        <v>39.08</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>472.12</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.0202020202020202</v>
+        <v>39.09</v>
       </c>
       <c r="AJ11" t="n">
-        <v>504.725</v>
+        <v>-0.35</v>
       </c>
       <c r="AK11" t="n">
-        <v>500.0833333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="AL11" t="n">
-        <v>496.8875</v>
+        <v>-0.3</v>
       </c>
       <c r="AM11" t="n">
-        <v>499.86</v>
+        <v>-0.26</v>
       </c>
       <c r="AN11" t="n">
-        <v>498.8916666666667</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="AO11" t="n">
-        <v>496.5142857142857</v>
+        <v>-0.2463768115942029</v>
       </c>
       <c r="AP11" t="n">
-        <v>495.65</v>
+        <v>-0.2658227848101266</v>
       </c>
       <c r="AQ11" t="n">
-        <v>495.0333333333334</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="AR11" t="n">
-        <v>495.085</v>
+        <v>-0.3604060913705584</v>
       </c>
       <c r="AS11" t="n">
-        <v>32.87323189161662</v>
+        <v>460.65</v>
       </c>
       <c r="AT11" t="n">
-        <v>40.14153778264549</v>
+        <v>456.7166666666666</v>
       </c>
       <c r="AU11" t="n">
-        <v>42.0264778889452</v>
+        <v>459.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>41.35094194815881</v>
+        <v>461.29</v>
       </c>
       <c r="AW11" t="n">
-        <v>41.95866931345125</v>
+        <v>462.575</v>
       </c>
       <c r="AX11" t="n">
-        <v>41.69163768744549</v>
+        <v>463.3642857142857</v>
       </c>
       <c r="AY11" t="n">
-        <v>41.44864292108971</v>
+        <v>464.49375</v>
       </c>
       <c r="AZ11" t="n">
-        <v>41.10500104745299</v>
+        <v>463.9111111111111</v>
       </c>
       <c r="BA11" t="n">
-        <v>40.42966454226401</v>
+        <v>463.81</v>
       </c>
       <c r="BB11" t="n">
-        <v>445</v>
+        <v>62.150442476301</v>
       </c>
       <c r="BC11" t="n">
-        <v>433</v>
+        <v>57.76160537550489</v>
       </c>
       <c r="BD11" t="n">
-        <v>424</v>
+        <v>56.3436775512568</v>
       </c>
       <c r="BE11" t="n">
-        <v>424</v>
+        <v>54.73943642384346</v>
       </c>
       <c r="BF11" t="n">
-        <v>424</v>
+        <v>52.5535698914292</v>
       </c>
       <c r="BG11" t="n">
-        <v>424</v>
+        <v>51.15190412798303</v>
       </c>
       <c r="BH11" t="n">
-        <v>424</v>
+        <v>49.65619257391268</v>
       </c>
       <c r="BI11" t="n">
-        <v>424</v>
+        <v>47.73215651352974</v>
       </c>
       <c r="BJ11" t="n">
-        <v>424</v>
+        <v>46.49466528538516</v>
       </c>
       <c r="BK11" t="n">
-        <v>636</v>
+        <v>363</v>
       </c>
       <c r="BL11" t="n">
-        <v>636</v>
+        <v>363</v>
       </c>
       <c r="BM11" t="n">
-        <v>636</v>
+        <v>363</v>
       </c>
       <c r="BN11" t="n">
-        <v>636</v>
+        <v>363</v>
       </c>
       <c r="BO11" t="n">
-        <v>636</v>
+        <v>363</v>
       </c>
       <c r="BP11" t="n">
-        <v>636</v>
+        <v>363</v>
       </c>
       <c r="BQ11" t="n">
-        <v>636</v>
+        <v>363</v>
       </c>
       <c r="BR11" t="n">
-        <v>636</v>
+        <v>363</v>
       </c>
       <c r="BS11" t="n">
-        <v>636</v>
+        <v>363</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.3636363636363636</v>
+        <v>658</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.6363636363636364</v>
+        <v>658</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.75</v>
+        <v>658</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.5882352941176471</v>
+        <v>658</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.5909090909090909</v>
+        <v>658</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.8695652173913043</v>
+        <v>658</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.5416666666666666</v>
+        <v>658</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.96</v>
+        <v>658</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.8</v>
+        <v>658</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0.8636363636363636</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>0.9259259259259259</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>0.9354838709677419</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0.02439024390243903</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>472.12</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>39.09</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S12_G2_479_42_ABS1</t>
+          <t>S11_G2_478_38_ABS1</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C12" t="n">
-        <v>42</v>
+        <v>56.33802816901409</v>
       </c>
       <c r="D12" t="n">
-        <v>62.26834692364714</v>
+        <v>38</v>
       </c>
       <c r="E12" t="n">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F12" t="n">
         <v>200</v>
       </c>
       <c r="G12" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="H12" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>479.2908983531565</v>
-      </c>
-      <c r="J12" t="n">
-        <v>46.86296483064424</v>
-      </c>
-      <c r="K12" t="n">
-        <v>477.7842724269808</v>
-      </c>
-      <c r="L12" t="n">
-        <v>52.08175784925633</v>
-      </c>
-      <c r="M12" t="n">
-        <v>477.3068289041678</v>
-      </c>
-      <c r="N12" t="n">
-        <v>46.17062635297545</v>
-      </c>
-      <c r="O12" t="n">
-        <v>486.0535110433636</v>
-      </c>
-      <c r="P12" t="n">
-        <v>45.25543839285633</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>478.9138651383424</v>
-      </c>
       <c r="R12" t="n">
-        <v>46.66115489853387</v>
+        <v>500.4</v>
       </c>
       <c r="S12" t="n">
-        <v>477.907584227149</v>
+        <v>23.79</v>
       </c>
       <c r="T12" t="n">
-        <v>51.44496853072018</v>
+        <v>498.95</v>
       </c>
       <c r="U12" t="n">
-        <v>478.9695379598764</v>
+        <v>39.06</v>
       </c>
       <c r="V12" t="n">
-        <v>49.13350067888805</v>
+        <v>495.8</v>
       </c>
       <c r="W12" t="n">
-        <v>479.7062422521552</v>
+        <v>33.51</v>
       </c>
       <c r="X12" t="n">
-        <v>49.02911837940848</v>
+        <v>499.7</v>
       </c>
       <c r="Y12" t="n">
-        <v>481.5451636067571</v>
+        <v>35.43</v>
       </c>
       <c r="Z12" t="n">
-        <v>46.84859038205705</v>
+        <v>495.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0.3</v>
+        <v>37.78</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0.2333333333333333</v>
+        <v>492.15</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.15</v>
+        <v>38.24</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0.14</v>
+        <v>489.69</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.1166666666666667</v>
+        <v>37.79</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.1142857142857143</v>
+        <v>489.85</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.08749999999999999</v>
+        <v>38.07</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0.07777777777777778</v>
+        <v>488.14</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0.08</v>
+        <v>36.63</v>
       </c>
       <c r="AJ12" t="n">
-        <v>478.6</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="AK12" t="n">
-        <v>477.9166666666667</v>
+        <v>0.06896551724137931</v>
       </c>
       <c r="AL12" t="n">
-        <v>479.7625</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>479.68</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AN12" t="n">
-        <v>480.5583333333333</v>
+        <v>0.03389830508474576</v>
       </c>
       <c r="AO12" t="n">
-        <v>479.5642857142857</v>
+        <v>-0.01449275362318841</v>
       </c>
       <c r="AP12" t="n">
-        <v>480.2375</v>
+        <v>-0.01265822784810127</v>
       </c>
       <c r="AQ12" t="n">
-        <v>479.6277777777778</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>479.505</v>
+        <v>0.0202020202020202</v>
       </c>
       <c r="AS12" t="n">
-        <v>49.16899429518566</v>
+        <v>504.725</v>
       </c>
       <c r="AT12" t="n">
-        <v>51.89357431855659</v>
+        <v>500.0833333333333</v>
       </c>
       <c r="AU12" t="n">
-        <v>53.02269413892508</v>
+        <v>496.8875</v>
       </c>
       <c r="AV12" t="n">
-        <v>50.53333157431835</v>
+        <v>499.86</v>
       </c>
       <c r="AW12" t="n">
-        <v>49.37978598464041</v>
+        <v>498.8916666666667</v>
       </c>
       <c r="AX12" t="n">
-        <v>49.7132076032525</v>
+        <v>496.5142857142857</v>
       </c>
       <c r="AY12" t="n">
-        <v>50.46328956528696</v>
+        <v>495.65</v>
       </c>
       <c r="AZ12" t="n">
-        <v>50.01022457186525</v>
+        <v>495.0333333333334</v>
       </c>
       <c r="BA12" t="n">
-        <v>49.53927709403923</v>
+        <v>495.085</v>
       </c>
       <c r="BB12" t="n">
-        <v>370</v>
+        <v>32.87323189161662</v>
       </c>
       <c r="BC12" t="n">
-        <v>370</v>
+        <v>40.14153778264549</v>
       </c>
       <c r="BD12" t="n">
-        <v>370</v>
+        <v>42.0264778889452</v>
       </c>
       <c r="BE12" t="n">
-        <v>370</v>
+        <v>41.35094194815881</v>
       </c>
       <c r="BF12" t="n">
-        <v>370</v>
+        <v>41.95866931345125</v>
       </c>
       <c r="BG12" t="n">
-        <v>370</v>
+        <v>41.69163768744549</v>
       </c>
       <c r="BH12" t="n">
-        <v>370</v>
+        <v>41.44864292108971</v>
       </c>
       <c r="BI12" t="n">
-        <v>370</v>
+        <v>41.10500104745299</v>
       </c>
       <c r="BJ12" t="n">
-        <v>370</v>
+        <v>40.42966454226401</v>
       </c>
       <c r="BK12" t="n">
-        <v>568</v>
+        <v>445</v>
       </c>
       <c r="BL12" t="n">
-        <v>568</v>
+        <v>433</v>
       </c>
       <c r="BM12" t="n">
-        <v>568</v>
+        <v>424</v>
       </c>
       <c r="BN12" t="n">
-        <v>568</v>
+        <v>424</v>
       </c>
       <c r="BO12" t="n">
-        <v>568</v>
+        <v>424</v>
       </c>
       <c r="BP12" t="n">
-        <v>568</v>
+        <v>424</v>
       </c>
       <c r="BQ12" t="n">
-        <v>568</v>
+        <v>424</v>
       </c>
       <c r="BR12" t="n">
-        <v>568</v>
+        <v>424</v>
       </c>
       <c r="BS12" t="n">
-        <v>568</v>
+        <v>424</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.6</v>
+        <v>636</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.625</v>
+        <v>636</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.9166666666666666</v>
+        <v>636</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.3846153846153846</v>
+        <v>636</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.3333333333333333</v>
+        <v>636</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.2631578947368421</v>
+        <v>636</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.25</v>
+        <v>636</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.2173913043478261</v>
+        <v>636</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.9642857142857143</v>
+        <v>636</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>0.5882352941176471</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>0.5909090909090909</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>0.8695652173913043</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>488.14</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>36.63</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S10_G2_480_38_ABS1</t>
+          <t>S12_G2_479_42_ABS1</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>62.26834692364714</v>
       </c>
       <c r="D13" t="n">
-        <v>56.33802816901409</v>
+        <v>42</v>
       </c>
       <c r="E13" t="n">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F13" t="n">
         <v>200</v>
       </c>
       <c r="G13" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H13" t="inlineStr">
+        <v>76</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>451.9913895961627</v>
-      </c>
-      <c r="J13" t="n">
-        <v>47.32724419274614</v>
-      </c>
-      <c r="K13" t="n">
-        <v>457.830458926974</v>
-      </c>
-      <c r="L13" t="n">
-        <v>45.68205262043752</v>
-      </c>
-      <c r="M13" t="n">
-        <v>461.1331102080725</v>
-      </c>
-      <c r="N13" t="n">
-        <v>49.55377596306899</v>
-      </c>
-      <c r="O13" t="n">
-        <v>468.8756671663194</v>
-      </c>
-      <c r="P13" t="n">
-        <v>47.53589776094446</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>470.4420324562511</v>
-      </c>
       <c r="R13" t="n">
-        <v>45.81243021210307</v>
+        <v>479.29</v>
       </c>
       <c r="S13" t="n">
-        <v>469.7523205491212</v>
+        <v>46.86</v>
       </c>
       <c r="T13" t="n">
-        <v>43.71223475633131</v>
+        <v>477.78</v>
       </c>
       <c r="U13" t="n">
-        <v>465.1746681403319</v>
+        <v>52.08</v>
       </c>
       <c r="V13" t="n">
-        <v>40.75813673361721</v>
+        <v>477.31</v>
       </c>
       <c r="W13" t="n">
-        <v>468.2956273871966</v>
+        <v>46.17</v>
       </c>
       <c r="X13" t="n">
-        <v>39.07763410812904</v>
+        <v>486.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>472.1205815020357</v>
+        <v>45.26</v>
       </c>
       <c r="Z13" t="n">
-        <v>39.09156035491998</v>
+        <v>478.91</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.35</v>
+        <v>46.66</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.4333333333333333</v>
+        <v>477.91</v>
       </c>
       <c r="AC13" t="n">
+        <v>51.44</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>478.97</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>49.13</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>479.71</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>49.03</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>481.55</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>46.85</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>-0.3</v>
       </c>
-      <c r="AD13" t="n">
-        <v>-0.26</v>
-      </c>
-      <c r="AE13" t="n">
+      <c r="AK13" t="n">
         <v>-0.2333333333333333</v>
       </c>
-      <c r="AF13" t="n">
-        <v>-0.2463768115942029</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>-0.2658227848101266</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>-0.3333333333333333</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>-0.3604060913705584</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>460.65</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>456.7166666666666</v>
-      </c>
       <c r="AL13" t="n">
-        <v>459.8</v>
+        <v>-0.15</v>
       </c>
       <c r="AM13" t="n">
-        <v>461.29</v>
+        <v>-0.14</v>
       </c>
       <c r="AN13" t="n">
-        <v>462.575</v>
+        <v>-0.1166666666666667</v>
       </c>
       <c r="AO13" t="n">
-        <v>463.3642857142857</v>
+        <v>-0.1142857142857143</v>
       </c>
       <c r="AP13" t="n">
-        <v>464.49375</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="AQ13" t="n">
-        <v>463.9111111111111</v>
+        <v>-0.07777777777777778</v>
       </c>
       <c r="AR13" t="n">
-        <v>463.81</v>
+        <v>-0.08</v>
       </c>
       <c r="AS13" t="n">
-        <v>62.150442476301</v>
+        <v>478.6</v>
       </c>
       <c r="AT13" t="n">
-        <v>57.76160537550489</v>
+        <v>477.9166666666667</v>
       </c>
       <c r="AU13" t="n">
-        <v>56.3436775512568</v>
+        <v>479.7625</v>
       </c>
       <c r="AV13" t="n">
-        <v>54.73943642384346</v>
+        <v>479.68</v>
       </c>
       <c r="AW13" t="n">
-        <v>52.5535698914292</v>
+        <v>480.5583333333333</v>
       </c>
       <c r="AX13" t="n">
-        <v>51.15190412798303</v>
+        <v>479.5642857142857</v>
       </c>
       <c r="AY13" t="n">
-        <v>49.65619257391268</v>
+        <v>480.2375</v>
       </c>
       <c r="AZ13" t="n">
-        <v>47.73215651352974</v>
+        <v>479.6277777777778</v>
       </c>
       <c r="BA13" t="n">
-        <v>46.49466528538516</v>
+        <v>479.505</v>
       </c>
       <c r="BB13" t="n">
-        <v>363</v>
+        <v>49.16899429518566</v>
       </c>
       <c r="BC13" t="n">
-        <v>363</v>
+        <v>51.89357431855659</v>
       </c>
       <c r="BD13" t="n">
-        <v>363</v>
+        <v>53.02269413892508</v>
       </c>
       <c r="BE13" t="n">
-        <v>363</v>
+        <v>50.53333157431835</v>
       </c>
       <c r="BF13" t="n">
-        <v>363</v>
+        <v>49.37978598464041</v>
       </c>
       <c r="BG13" t="n">
-        <v>363</v>
+        <v>49.7132076032525</v>
       </c>
       <c r="BH13" t="n">
-        <v>363</v>
+        <v>50.46328956528696</v>
       </c>
       <c r="BI13" t="n">
-        <v>363</v>
+        <v>50.01022457186525</v>
       </c>
       <c r="BJ13" t="n">
-        <v>363</v>
+        <v>49.53927709403923</v>
       </c>
       <c r="BK13" t="n">
-        <v>658</v>
+        <v>370</v>
       </c>
       <c r="BL13" t="n">
-        <v>658</v>
+        <v>370</v>
       </c>
       <c r="BM13" t="n">
-        <v>658</v>
+        <v>370</v>
       </c>
       <c r="BN13" t="n">
-        <v>658</v>
+        <v>370</v>
       </c>
       <c r="BO13" t="n">
-        <v>658</v>
+        <v>370</v>
       </c>
       <c r="BP13" t="n">
-        <v>658</v>
+        <v>370</v>
       </c>
       <c r="BQ13" t="n">
-        <v>658</v>
+        <v>370</v>
       </c>
       <c r="BR13" t="n">
-        <v>658</v>
+        <v>370</v>
       </c>
       <c r="BS13" t="n">
-        <v>658</v>
+        <v>370</v>
       </c>
       <c r="BT13" t="n">
-        <v>1</v>
+        <v>568</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.875</v>
+        <v>568</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.08333333333333333</v>
+        <v>568</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.9444444444444444</v>
+        <v>568</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.8636363636363636</v>
+        <v>568</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.9259259259259259</v>
+        <v>568</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.9354838709677419</v>
+        <v>568</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.9411764705882353</v>
+        <v>568</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.02439024390243903</v>
+        <v>568</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>0.3846153846153846</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>0.2631578947368421</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>0.2173913043478261</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0.9642857142857143</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>481.55</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>46.85</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S14_G2_480_39_ABS1</t>
+          <t>S13_G2_481_40_ABS1</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>59.30318754633062</v>
       </c>
       <c r="D14" t="n">
-        <v>57.82060785767235</v>
+        <v>40</v>
       </c>
       <c r="E14" t="n">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F14" t="n">
         <v>200</v>
       </c>
       <c r="G14" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="H14" t="inlineStr">
+        <v>74.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="L14" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>471.0334340617805</v>
-      </c>
-      <c r="J14" t="n">
-        <v>69.56325447162078</v>
-      </c>
-      <c r="K14" t="n">
-        <v>468.1959079596524</v>
-      </c>
-      <c r="L14" t="n">
-        <v>67.25730522533892</v>
-      </c>
-      <c r="M14" t="n">
-        <v>474.4248267815889</v>
-      </c>
-      <c r="N14" t="n">
-        <v>49.78825908700425</v>
-      </c>
-      <c r="O14" t="n">
-        <v>477.5045414586241</v>
-      </c>
-      <c r="P14" t="n">
-        <v>47.4073688255769</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>472.228032284402</v>
-      </c>
       <c r="R14" t="n">
-        <v>42.83491281962215</v>
+        <v>456.07</v>
       </c>
       <c r="S14" t="n">
-        <v>473.087585726514</v>
+        <v>10.07</v>
       </c>
       <c r="T14" t="n">
-        <v>39.71812917790595</v>
+        <v>463</v>
       </c>
       <c r="U14" t="n">
-        <v>470.5216317623156</v>
+        <v>36.56</v>
       </c>
       <c r="V14" t="n">
-        <v>37.56669887764475</v>
+        <v>470.88</v>
       </c>
       <c r="W14" t="n">
-        <v>471.0663654559909</v>
+        <v>51.13</v>
       </c>
       <c r="X14" t="n">
-        <v>36.91955331936975</v>
+        <v>472.75</v>
       </c>
       <c r="Y14" t="n">
-        <v>471.1601466981423</v>
+        <v>63.36</v>
       </c>
       <c r="Z14" t="n">
-        <v>37.25527214771613</v>
+        <v>474.08</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0.3</v>
+        <v>53.64</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.3333333333333333</v>
+        <v>474.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.35</v>
+        <v>53.95</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.3</v>
+        <v>470.77</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.2666666666666667</v>
+        <v>50.75</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.2857142857142857</v>
+        <v>469.16</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0.2875</v>
+        <v>52.74</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0.3222222222222222</v>
+        <v>470.25</v>
       </c>
       <c r="AI14" t="n">
-        <v>-0.3636363636363636</v>
+        <v>55.41</v>
       </c>
       <c r="AJ14" t="n">
-        <v>467.575</v>
+        <v>-0.95</v>
       </c>
       <c r="AK14" t="n">
-        <v>457.8166666666667</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="AL14" t="n">
-        <v>456.9125</v>
+        <v>-0.375</v>
       </c>
       <c r="AM14" t="n">
-        <v>461.49</v>
+        <v>-0.24</v>
       </c>
       <c r="AN14" t="n">
-        <v>464.5916666666666</v>
+        <v>-0.1833333333333333</v>
       </c>
       <c r="AO14" t="n">
-        <v>465.5</v>
+        <v>-0.1571428571428571</v>
       </c>
       <c r="AP14" t="n">
-        <v>467.1375</v>
+        <v>-0.1375</v>
       </c>
       <c r="AQ14" t="n">
-        <v>467.1722222222222</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="AR14" t="n">
-        <v>466.955</v>
+        <v>-0.12</v>
       </c>
       <c r="AS14" t="n">
-        <v>53.83766687923985</v>
+        <v>453.1</v>
       </c>
       <c r="AT14" t="n">
-        <v>61.66914184221762</v>
+        <v>465</v>
       </c>
       <c r="AU14" t="n">
-        <v>60.63398258196472</v>
+        <v>473.5875</v>
       </c>
       <c r="AV14" t="n">
-        <v>58.42850246241127</v>
+        <v>477.22</v>
       </c>
       <c r="AW14" t="n">
-        <v>55.95883841916505</v>
+        <v>477.05</v>
       </c>
       <c r="AX14" t="n">
-        <v>53.05691014642404</v>
+        <v>476.7428571428571</v>
       </c>
       <c r="AY14" t="n">
-        <v>50.79474474539665</v>
+        <v>475.7625</v>
       </c>
       <c r="AZ14" t="n">
-        <v>48.93599340584887</v>
+        <v>473.8888888888889</v>
       </c>
       <c r="BA14" t="n">
-        <v>47.37513034282861</v>
+        <v>473.425</v>
       </c>
       <c r="BB14" t="n">
-        <v>298</v>
+        <v>21.99295341694698</v>
       </c>
       <c r="BC14" t="n">
-        <v>298</v>
+        <v>31.65385705829017</v>
       </c>
       <c r="BD14" t="n">
-        <v>298</v>
+        <v>46.03414323901337</v>
       </c>
       <c r="BE14" t="n">
-        <v>298</v>
+        <v>51.47029823111578</v>
       </c>
       <c r="BF14" t="n">
-        <v>298</v>
+        <v>55.12271915160451</v>
       </c>
       <c r="BG14" t="n">
-        <v>298</v>
+        <v>56.00935781871907</v>
       </c>
       <c r="BH14" t="n">
-        <v>298</v>
+        <v>55.91695712169967</v>
       </c>
       <c r="BI14" t="n">
-        <v>298</v>
+        <v>55.62102808679554</v>
       </c>
       <c r="BJ14" t="n">
-        <v>298</v>
+        <v>55.07680432813799</v>
       </c>
       <c r="BK14" t="n">
-        <v>560</v>
+        <v>347</v>
       </c>
       <c r="BL14" t="n">
-        <v>560</v>
+        <v>347</v>
       </c>
       <c r="BM14" t="n">
-        <v>560</v>
+        <v>347</v>
       </c>
       <c r="BN14" t="n">
-        <v>560</v>
+        <v>347</v>
       </c>
       <c r="BO14" t="n">
-        <v>560</v>
+        <v>347</v>
       </c>
       <c r="BP14" t="n">
-        <v>560</v>
+        <v>347</v>
       </c>
       <c r="BQ14" t="n">
-        <v>560</v>
+        <v>347</v>
       </c>
       <c r="BR14" t="n">
-        <v>560</v>
+        <v>347</v>
       </c>
       <c r="BS14" t="n">
-        <v>560</v>
+        <v>347</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.5</v>
+        <v>502</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.625</v>
+        <v>532</v>
       </c>
       <c r="BV14" t="n">
+        <v>567</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>567</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>567</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>567</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>567</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>567</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>567</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>0.5384615384615384</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="CI14" t="n">
         <v>1</v>
       </c>
-      <c r="BW14" t="n">
-        <v>0.9166666666666666</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="BZ14" t="n">
-        <v>0.9130434782608695</v>
-      </c>
-      <c r="CA14" t="n">
-        <v>0.8214285714285714</v>
-      </c>
-      <c r="CB14" t="n">
-        <v>0.7272727272727273</v>
+      <c r="CJ14" t="n">
+        <v>0.9523809523809523</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>470.25</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>55.41</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S15_G2_481_42_ABS1</t>
+          <t>S14_G2_480_39_ABS1</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C15" t="n">
-        <v>42</v>
+        <v>57.82060785767235</v>
       </c>
       <c r="D15" t="n">
-        <v>62.26834692364714</v>
+        <v>39</v>
       </c>
       <c r="E15" t="n">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F15" t="n">
         <v>200</v>
       </c>
       <c r="G15" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>ABS1</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>471.03</v>
+      </c>
+      <c r="S15" t="n">
+        <v>69.56</v>
+      </c>
+      <c r="T15" t="n">
+        <v>468.2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>67.26000000000001</v>
+      </c>
+      <c r="V15" t="n">
+        <v>474.42</v>
+      </c>
+      <c r="W15" t="n">
+        <v>49.79</v>
+      </c>
+      <c r="X15" t="n">
+        <v>477.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>47.41</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>472.23</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>42.83</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>473.09</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>39.72</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>470.52</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>37.57</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>471.07</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>36.92</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>471.16</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>37.26</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>-0.2666666666666667</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>-0.2875</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>-0.3222222222222222</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>-0.3636363636363636</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>467.575</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>457.8166666666667</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>456.9125</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>461.49</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>464.5916666666666</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>465.5</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>467.1375</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>467.1722222222222</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>466.955</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>53.83766687923985</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>61.66914184221762</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>60.63398258196472</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>58.42850246241127</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>55.95883841916505</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>53.05691014642404</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>50.79474474539665</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>48.93599340584887</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>47.37513034282861</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>298</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>298</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>298</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>298</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>298</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>298</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>298</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>298</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>298</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>560</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>560</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>560</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>560</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>560</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>560</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>560</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>560</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>560</v>
+      </c>
+      <c r="CC15" t="n">
         <v>0.5</v>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>ABS1</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>496.4533865414144</v>
-      </c>
-      <c r="J15" t="n">
-        <v>36.43976493397722</v>
-      </c>
-      <c r="K15" t="n">
-        <v>498.1754385788206</v>
-      </c>
-      <c r="L15" t="n">
-        <v>33.22192185988961</v>
-      </c>
-      <c r="M15" t="n">
-        <v>494.7938558488974</v>
-      </c>
-      <c r="N15" t="n">
-        <v>31.47421824767036</v>
-      </c>
-      <c r="O15" t="n">
-        <v>493.1248440693157</v>
-      </c>
-      <c r="P15" t="n">
-        <v>33.92313199539164</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>485.8759464814168</v>
-      </c>
-      <c r="R15" t="n">
-        <v>47.96858040649108</v>
-      </c>
-      <c r="S15" t="n">
-        <v>487.4007187090078</v>
-      </c>
-      <c r="T15" t="n">
-        <v>50.86870393577949</v>
-      </c>
-      <c r="U15" t="n">
-        <v>490.5897311652748</v>
-      </c>
-      <c r="V15" t="n">
-        <v>57.2262465256178</v>
-      </c>
-      <c r="W15" t="n">
-        <v>492.9177452231904</v>
-      </c>
-      <c r="X15" t="n">
-        <v>55.06434293923911</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>491.9739648317821</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>50.4995295973746</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>-0.08333333333333333</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>-0.08571428571428572</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>-0.01111111111111111</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>498.5</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>496.3833333333333</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>495.4875</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>494.11</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>490.4083333333334</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>488.6071428571428</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>490.29375</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>492.3388888888889</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>491.43</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>43.58440087921365</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>43.49984355016566</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>40.20758440580583</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>38.68795549004884</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>39.66558034226764</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>43.4305186358578</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>47.35168910332028</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>49.65717626205691</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>50.53607721222532</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>363</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>363</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>363</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>363</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>363</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>363</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>363</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>363</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>363</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>565</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>565</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>565</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>565</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>565</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>565</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>574</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>574</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>574</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BU15" t="n">
+      <c r="CD15" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="CE15" t="n">
         <v>1</v>
       </c>
-      <c r="BV15" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>1</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>1</v>
-      </c>
-      <c r="BZ15" t="n">
-        <v>0.8947368421052632</v>
-      </c>
-      <c r="CA15" t="n">
-        <v>0.9473684210526315</v>
-      </c>
-      <c r="CB15" t="n">
-        <v>1</v>
+      <c r="CF15" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>0.9130434782608695</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>0.8214285714285714</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>471.16</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>37.26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S13_G2_481_40_ABS1</t>
+          <t>S15_G2_481_42_ABS1</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>481</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>62.26834692364714</v>
       </c>
       <c r="D16" t="n">
-        <v>59.30318754633062</v>
+        <v>42</v>
       </c>
       <c r="E16" t="n">
         <v>481</v>
@@ -4296,966 +4813,1098 @@
         <v>200</v>
       </c>
       <c r="G16" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="H16" t="inlineStr">
+        <v>76</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>456.0724161196923</v>
-      </c>
-      <c r="J16" t="n">
-        <v>10.06546752857113</v>
-      </c>
-      <c r="K16" t="n">
-        <v>462.9994714681029</v>
-      </c>
-      <c r="L16" t="n">
-        <v>36.5638618407955</v>
-      </c>
-      <c r="M16" t="n">
-        <v>470.8833361576826</v>
-      </c>
-      <c r="N16" t="n">
-        <v>51.12664519386517</v>
-      </c>
-      <c r="O16" t="n">
-        <v>472.7532284707058</v>
-      </c>
-      <c r="P16" t="n">
-        <v>63.3613893116908</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>474.0818280658199</v>
-      </c>
       <c r="R16" t="n">
-        <v>53.64203766707907</v>
+        <v>496.45</v>
       </c>
       <c r="S16" t="n">
-        <v>474.1950472121116</v>
+        <v>36.44</v>
       </c>
       <c r="T16" t="n">
-        <v>53.94671859087052</v>
+        <v>498.18</v>
       </c>
       <c r="U16" t="n">
-        <v>470.769169215628</v>
+        <v>33.22</v>
       </c>
       <c r="V16" t="n">
-        <v>50.74837754621174</v>
+        <v>494.79</v>
       </c>
       <c r="W16" t="n">
-        <v>469.1611619976686</v>
+        <v>31.47</v>
       </c>
       <c r="X16" t="n">
-        <v>52.73538056316442</v>
+        <v>493.12</v>
       </c>
       <c r="Y16" t="n">
-        <v>470.2532883505966</v>
+        <v>33.92</v>
       </c>
       <c r="Z16" t="n">
-        <v>55.41049269948159</v>
+        <v>485.88</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0.95</v>
+        <v>47.97</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0.6333333333333333</v>
+        <v>487.4</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.375</v>
+        <v>50.87</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0.24</v>
+        <v>490.59</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0.1833333333333333</v>
+        <v>57.23</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.1571428571428571</v>
+        <v>492.92</v>
       </c>
       <c r="AG16" t="n">
-        <v>-0.1375</v>
+        <v>55.06</v>
       </c>
       <c r="AH16" t="n">
-        <v>-0.1333333333333333</v>
+        <v>491.97</v>
       </c>
       <c r="AI16" t="n">
-        <v>-0.12</v>
+        <v>50.5</v>
       </c>
       <c r="AJ16" t="n">
-        <v>453.1</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>465</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>473.5875</v>
+        <v>0.025</v>
       </c>
       <c r="AM16" t="n">
-        <v>477.22</v>
+        <v>-0.02</v>
       </c>
       <c r="AN16" t="n">
-        <v>477.05</v>
+        <v>-0.08333333333333333</v>
       </c>
       <c r="AO16" t="n">
-        <v>476.7428571428571</v>
+        <v>-0.08571428571428572</v>
       </c>
       <c r="AP16" t="n">
-        <v>475.7625</v>
+        <v>-0.05</v>
       </c>
       <c r="AQ16" t="n">
-        <v>473.8888888888889</v>
+        <v>-0.01111111111111111</v>
       </c>
       <c r="AR16" t="n">
-        <v>473.425</v>
+        <v>-0.02</v>
       </c>
       <c r="AS16" t="n">
-        <v>21.99295341694698</v>
+        <v>498.5</v>
       </c>
       <c r="AT16" t="n">
-        <v>31.65385705829017</v>
+        <v>496.3833333333333</v>
       </c>
       <c r="AU16" t="n">
-        <v>46.03414323901337</v>
+        <v>495.4875</v>
       </c>
       <c r="AV16" t="n">
-        <v>51.47029823111578</v>
+        <v>494.11</v>
       </c>
       <c r="AW16" t="n">
-        <v>55.12271915160451</v>
+        <v>490.4083333333334</v>
       </c>
       <c r="AX16" t="n">
-        <v>56.00935781871907</v>
+        <v>488.6071428571428</v>
       </c>
       <c r="AY16" t="n">
-        <v>55.91695712169967</v>
+        <v>490.29375</v>
       </c>
       <c r="AZ16" t="n">
-        <v>55.62102808679554</v>
+        <v>492.3388888888889</v>
       </c>
       <c r="BA16" t="n">
-        <v>55.07680432813799</v>
+        <v>491.43</v>
       </c>
       <c r="BB16" t="n">
-        <v>347</v>
+        <v>43.58440087921365</v>
       </c>
       <c r="BC16" t="n">
-        <v>347</v>
+        <v>43.49984355016566</v>
       </c>
       <c r="BD16" t="n">
-        <v>347</v>
+        <v>40.20758440580583</v>
       </c>
       <c r="BE16" t="n">
-        <v>347</v>
+        <v>38.68795549004884</v>
       </c>
       <c r="BF16" t="n">
-        <v>347</v>
+        <v>39.66558034226764</v>
       </c>
       <c r="BG16" t="n">
-        <v>347</v>
+        <v>43.4305186358578</v>
       </c>
       <c r="BH16" t="n">
-        <v>347</v>
+        <v>47.35168910332028</v>
       </c>
       <c r="BI16" t="n">
-        <v>347</v>
+        <v>49.65717626205691</v>
       </c>
       <c r="BJ16" t="n">
-        <v>347</v>
+        <v>50.53607721222532</v>
       </c>
       <c r="BK16" t="n">
-        <v>502</v>
+        <v>363</v>
       </c>
       <c r="BL16" t="n">
-        <v>532</v>
+        <v>363</v>
       </c>
       <c r="BM16" t="n">
-        <v>567</v>
+        <v>363</v>
       </c>
       <c r="BN16" t="n">
-        <v>567</v>
+        <v>363</v>
       </c>
       <c r="BO16" t="n">
-        <v>567</v>
+        <v>363</v>
       </c>
       <c r="BP16" t="n">
-        <v>567</v>
+        <v>363</v>
       </c>
       <c r="BQ16" t="n">
-        <v>567</v>
+        <v>363</v>
       </c>
       <c r="BR16" t="n">
-        <v>567</v>
+        <v>363</v>
       </c>
       <c r="BS16" t="n">
-        <v>567</v>
+        <v>363</v>
       </c>
       <c r="BT16" t="n">
-        <v>0.3</v>
+        <v>565</v>
       </c>
       <c r="BU16" t="n">
-        <v>0.5384615384615384</v>
+        <v>565</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.4375</v>
+        <v>565</v>
       </c>
       <c r="BW16" t="n">
-        <v>0.5625</v>
+        <v>565</v>
       </c>
       <c r="BX16" t="n">
-        <v>0.75</v>
+        <v>565</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.8888888888888888</v>
+        <v>565</v>
       </c>
       <c r="BZ16" t="n">
+        <v>574</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>574</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>574</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CD16" t="n">
         <v>1</v>
       </c>
-      <c r="CA16" t="n">
-        <v>0.9523809523809523</v>
-      </c>
-      <c r="CB16" t="n">
-        <v>0.92</v>
+      <c r="CE16" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>0.9473684210526315</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>491.97</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>50.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S17_G2_481_40_ABS1</t>
+          <t>S16_G2_479_38_ABS1</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>56.33802816901409</v>
       </c>
       <c r="D17" t="n">
-        <v>59.30318754633062</v>
+        <v>38</v>
       </c>
       <c r="E17" t="n">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="F17" t="n">
         <v>200</v>
       </c>
       <c r="G17" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="H17" t="inlineStr">
+        <v>75.5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>470.8197450282959</v>
-      </c>
-      <c r="J17" t="n">
-        <v>54.66185707519629</v>
-      </c>
-      <c r="K17" t="n">
-        <v>474.5036022313715</v>
-      </c>
-      <c r="L17" t="n">
-        <v>43.30661345748265</v>
-      </c>
-      <c r="M17" t="n">
-        <v>477.75591326079</v>
-      </c>
-      <c r="N17" t="n">
-        <v>43.01558338441785</v>
-      </c>
-      <c r="O17" t="n">
-        <v>482.1462921569033</v>
-      </c>
-      <c r="P17" t="n">
-        <v>47.95555188615108</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>482.1448383968102</v>
-      </c>
       <c r="R17" t="n">
-        <v>47.98192856555291</v>
+        <v>466.66</v>
       </c>
       <c r="S17" t="n">
-        <v>482.1006242367245</v>
+        <v>53.62</v>
       </c>
       <c r="T17" t="n">
-        <v>45.33709451059441</v>
+        <v>476.52</v>
       </c>
       <c r="U17" t="n">
-        <v>481.8092604402481</v>
+        <v>52.08</v>
       </c>
       <c r="V17" t="n">
-        <v>46.49979283437872</v>
+        <v>476.42</v>
       </c>
       <c r="W17" t="n">
-        <v>477.4124795494223</v>
+        <v>52.69</v>
       </c>
       <c r="X17" t="n">
-        <v>47.94809338168842</v>
+        <v>467.82</v>
       </c>
       <c r="Y17" t="n">
-        <v>476.5266954748109</v>
+        <v>58.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>48.97670967982665</v>
+        <v>469.86</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.2631578947368421</v>
+        <v>55.43</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0.1379310344827586</v>
+        <v>467.39</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.1282051282051282</v>
+        <v>49.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0.08163265306122448</v>
+        <v>471.75</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0.06779661016949153</v>
+        <v>48.45</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0.08695652173913043</v>
+        <v>471.13</v>
       </c>
       <c r="AG17" t="n">
-        <v>-0.06329113924050633</v>
+        <v>49.15</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0.05617977528089887</v>
+        <v>470.32</v>
       </c>
       <c r="AI17" t="n">
-        <v>-0.06060606060606061</v>
+        <v>52.23</v>
       </c>
       <c r="AJ17" t="n">
-        <v>470.025</v>
+        <v>-0.2</v>
       </c>
       <c r="AK17" t="n">
-        <v>472.7666666666667</v>
+        <v>-0.1</v>
       </c>
       <c r="AL17" t="n">
-        <v>473.925</v>
+        <v>-0.1</v>
       </c>
       <c r="AM17" t="n">
-        <v>476.76</v>
+        <v>-0.12</v>
       </c>
       <c r="AN17" t="n">
-        <v>477.6583333333334</v>
+        <v>-0.1</v>
       </c>
       <c r="AO17" t="n">
-        <v>477.1714285714286</v>
+        <v>-0.1</v>
       </c>
       <c r="AP17" t="n">
-        <v>478.56875</v>
+        <v>-0.1069182389937107</v>
       </c>
       <c r="AQ17" t="n">
-        <v>479.2</v>
+        <v>-0.0898876404494382</v>
       </c>
       <c r="AR17" t="n">
-        <v>478.285</v>
+        <v>-0.09090909090909091</v>
       </c>
       <c r="AS17" t="n">
-        <v>49.33329884570867</v>
+        <v>465.625</v>
       </c>
       <c r="AT17" t="n">
-        <v>52.06065906442428</v>
+        <v>470.9166666666667</v>
       </c>
       <c r="AU17" t="n">
-        <v>49.67639655812406</v>
+        <v>472.6</v>
       </c>
       <c r="AV17" t="n">
-        <v>49.80303605203201</v>
+        <v>470.1</v>
       </c>
       <c r="AW17" t="n">
-        <v>50.06886854345944</v>
+        <v>469.65</v>
       </c>
       <c r="AX17" t="n">
-        <v>49.08897793906531</v>
+        <v>470.3428571428572</v>
       </c>
       <c r="AY17" t="n">
-        <v>48.42902304855529</v>
+        <v>470.125</v>
       </c>
       <c r="AZ17" t="n">
-        <v>48.35911955820168</v>
+        <v>470.7555555555555</v>
       </c>
       <c r="BA17" t="n">
-        <v>49.0005487214174</v>
+        <v>470.11</v>
       </c>
       <c r="BB17" t="n">
-        <v>366</v>
+        <v>55.65010669351857</v>
       </c>
       <c r="BC17" t="n">
-        <v>366</v>
+        <v>53.56967166431228</v>
       </c>
       <c r="BD17" t="n">
-        <v>366</v>
+        <v>53.16615464748227</v>
       </c>
       <c r="BE17" t="n">
-        <v>366</v>
+        <v>54.75792180132478</v>
       </c>
       <c r="BF17" t="n">
-        <v>366</v>
+        <v>56.56996405631997</v>
       </c>
       <c r="BG17" t="n">
-        <v>366</v>
+        <v>55.44350682433058</v>
       </c>
       <c r="BH17" t="n">
-        <v>366</v>
+        <v>54.0691397656741</v>
       </c>
       <c r="BI17" t="n">
-        <v>366</v>
+        <v>52.73651720500303</v>
       </c>
       <c r="BJ17" t="n">
-        <v>366</v>
+        <v>52.48797862368106</v>
       </c>
       <c r="BK17" t="n">
+        <v>360</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>360</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>360</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>360</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>360</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>360</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>360</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>360</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>360</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>539</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>539</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>545</v>
+      </c>
+      <c r="BW17" t="n">
         <v>546</v>
       </c>
-      <c r="BL17" t="n">
+      <c r="BX17" t="n">
         <v>546</v>
       </c>
-      <c r="BM17" t="n">
+      <c r="BY17" t="n">
         <v>546</v>
       </c>
-      <c r="BN17" t="n">
+      <c r="BZ17" t="n">
         <v>546</v>
       </c>
-      <c r="BO17" t="n">
-        <v>548</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>548</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>548</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>548</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>548</v>
-      </c>
-      <c r="BT17" t="n">
+      <c r="CA17" t="n">
+        <v>546</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>546</v>
+      </c>
+      <c r="CC17" t="n">
         <v>1</v>
       </c>
-      <c r="BU17" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>1</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BX17" t="n">
-        <v>0.8421052631578947</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>0.9090909090909091</v>
-      </c>
-      <c r="BZ17" t="n">
-        <v>0.3703703703703703</v>
-      </c>
-      <c r="CA17" t="n">
-        <v>0.8387096774193549</v>
-      </c>
-      <c r="CB17" t="n">
-        <v>0.8484848484848485</v>
+      <c r="CD17" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>0.9523809523809523</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>470.32</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>52.23</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S18_G2_480_41_ABS1</t>
+          <t>S17_G2_481_40_ABS1</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C18" t="n">
-        <v>41</v>
+        <v>59.30318754633062</v>
       </c>
       <c r="D18" t="n">
-        <v>60.78576723498888</v>
+        <v>40</v>
       </c>
       <c r="E18" t="n">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F18" t="n">
         <v>200</v>
       </c>
       <c r="G18" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="H18" t="inlineStr">
+        <v>74.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="P18" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>476.3005488845355</v>
-      </c>
-      <c r="J18" t="n">
-        <v>68.87055472411157</v>
-      </c>
-      <c r="K18" t="n">
-        <v>475.1169274937627</v>
-      </c>
-      <c r="L18" t="n">
-        <v>58.298729760839</v>
-      </c>
-      <c r="M18" t="n">
-        <v>482.7433312798851</v>
-      </c>
-      <c r="N18" t="n">
-        <v>55.88492602643774</v>
-      </c>
-      <c r="O18" t="n">
-        <v>479.1709756990573</v>
-      </c>
-      <c r="P18" t="n">
-        <v>56.9051678648642</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>479.2222429621849</v>
-      </c>
       <c r="R18" t="n">
-        <v>56.61072767388428</v>
+        <v>470.82</v>
       </c>
       <c r="S18" t="n">
-        <v>476.4997778592379</v>
+        <v>54.66</v>
       </c>
       <c r="T18" t="n">
-        <v>50.43309786438655</v>
+        <v>474.5</v>
       </c>
       <c r="U18" t="n">
-        <v>483.2065471322566</v>
+        <v>43.31</v>
       </c>
       <c r="V18" t="n">
-        <v>49.98374001647736</v>
+        <v>477.76</v>
       </c>
       <c r="W18" t="n">
-        <v>481.9088816115056</v>
+        <v>43.02</v>
       </c>
       <c r="X18" t="n">
-        <v>49.86077952200398</v>
+        <v>482.15</v>
       </c>
       <c r="Y18" t="n">
-        <v>474.702974802015</v>
+        <v>47.96</v>
       </c>
       <c r="Z18" t="n">
-        <v>50.82288427238043</v>
+        <v>482.14</v>
       </c>
       <c r="AA18" t="n">
-        <v>-0.55</v>
+        <v>47.98</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0.2666666666666667</v>
+        <v>482.1</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.125</v>
+        <v>45.34</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0.1</v>
+        <v>481.81</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0.08333333333333333</v>
+        <v>46.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>-0.01428571428571429</v>
+        <v>477.41</v>
       </c>
       <c r="AG18" t="n">
-        <v>-0.05</v>
+        <v>47.95</v>
       </c>
       <c r="AH18" t="n">
-        <v>-0.04444444444444445</v>
+        <v>476.53</v>
       </c>
       <c r="AI18" t="n">
-        <v>-0.03</v>
+        <v>48.98</v>
       </c>
       <c r="AJ18" t="n">
-        <v>464.1</v>
+        <v>-0.2631578947368421</v>
       </c>
       <c r="AK18" t="n">
-        <v>474.8166666666667</v>
+        <v>-0.1379310344827586</v>
       </c>
       <c r="AL18" t="n">
-        <v>481.5125</v>
+        <v>-0.1282051282051282</v>
       </c>
       <c r="AM18" t="n">
-        <v>480.74</v>
+        <v>-0.08163265306122448</v>
       </c>
       <c r="AN18" t="n">
-        <v>480.5</v>
+        <v>-0.06779661016949153</v>
       </c>
       <c r="AO18" t="n">
-        <v>481.75</v>
+        <v>-0.08695652173913043</v>
       </c>
       <c r="AP18" t="n">
-        <v>479.55</v>
+        <v>-0.06329113924050633</v>
       </c>
       <c r="AQ18" t="n">
-        <v>479.9555555555556</v>
+        <v>-0.05617977528089887</v>
       </c>
       <c r="AR18" t="n">
-        <v>479.855</v>
+        <v>-0.06060606060606061</v>
       </c>
       <c r="AS18" t="n">
-        <v>43.8</v>
+        <v>470.025</v>
       </c>
       <c r="AT18" t="n">
-        <v>57.04106464254989</v>
+        <v>472.7666666666667</v>
       </c>
       <c r="AU18" t="n">
-        <v>61.35694617359961</v>
+        <v>473.925</v>
       </c>
       <c r="AV18" t="n">
-        <v>60.6426615510896</v>
+        <v>476.76</v>
       </c>
       <c r="AW18" t="n">
-        <v>60.72286774079981</v>
+        <v>477.6583333333334</v>
       </c>
       <c r="AX18" t="n">
-        <v>58.48004849030626</v>
+        <v>477.1714285714286</v>
       </c>
       <c r="AY18" t="n">
-        <v>56.82877792104982</v>
+        <v>478.56875</v>
       </c>
       <c r="AZ18" t="n">
-        <v>55.67403366643519</v>
+        <v>479.2</v>
       </c>
       <c r="BA18" t="n">
-        <v>54.64488974277467</v>
+        <v>478.285</v>
       </c>
       <c r="BB18" t="n">
-        <v>368</v>
+        <v>49.33329884570867</v>
       </c>
       <c r="BC18" t="n">
-        <v>368</v>
+        <v>52.06065906442428</v>
       </c>
       <c r="BD18" t="n">
-        <v>368</v>
+        <v>49.67639655812406</v>
       </c>
       <c r="BE18" t="n">
-        <v>368</v>
+        <v>49.80303605203201</v>
       </c>
       <c r="BF18" t="n">
-        <v>368</v>
+        <v>50.06886854345944</v>
       </c>
       <c r="BG18" t="n">
-        <v>368</v>
+        <v>49.08897793906531</v>
       </c>
       <c r="BH18" t="n">
-        <v>368</v>
+        <v>48.42902304855529</v>
       </c>
       <c r="BI18" t="n">
-        <v>368</v>
+        <v>48.35911955820168</v>
       </c>
       <c r="BJ18" t="n">
-        <v>368</v>
+        <v>49.0005487214174</v>
       </c>
       <c r="BK18" t="n">
-        <v>541</v>
+        <v>366</v>
       </c>
       <c r="BL18" t="n">
-        <v>564</v>
+        <v>366</v>
       </c>
       <c r="BM18" t="n">
-        <v>572</v>
+        <v>366</v>
       </c>
       <c r="BN18" t="n">
-        <v>572</v>
+        <v>366</v>
       </c>
       <c r="BO18" t="n">
-        <v>572</v>
+        <v>366</v>
       </c>
       <c r="BP18" t="n">
-        <v>572</v>
+        <v>366</v>
       </c>
       <c r="BQ18" t="n">
-        <v>572</v>
+        <v>366</v>
       </c>
       <c r="BR18" t="n">
-        <v>572</v>
+        <v>366</v>
       </c>
       <c r="BS18" t="n">
-        <v>572</v>
+        <v>366</v>
       </c>
       <c r="BT18" t="n">
+        <v>546</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>546</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>546</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>546</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>548</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>548</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>548</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>548</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>548</v>
+      </c>
+      <c r="CC18" t="n">
         <v>1</v>
       </c>
-      <c r="BU18" t="n">
+      <c r="CD18" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CE18" t="n">
         <v>1</v>
       </c>
-      <c r="BV18" t="n">
-        <v>1</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>1</v>
-      </c>
-      <c r="BX18" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="BY18" t="n">
-        <v>0.8947368421052632</v>
-      </c>
-      <c r="BZ18" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="CA18" t="n">
-        <v>0.9565217391304348</v>
-      </c>
-      <c r="CB18" t="n">
-        <v>0.9615384615384616</v>
+      <c r="CF18" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>0.3703703703703703</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>0.8387096774193549</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>476.53</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>48.98</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S16_G2_479_38_ABS1</t>
+          <t>S18_G2_480_41_ABS1</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C19" t="n">
-        <v>38</v>
+        <v>60.78576723498888</v>
       </c>
       <c r="D19" t="n">
-        <v>56.33802816901409</v>
+        <v>41</v>
       </c>
       <c r="E19" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F19" t="n">
         <v>200</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H19" t="inlineStr">
+        <v>76</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>466.6626809085331</v>
-      </c>
-      <c r="J19" t="n">
-        <v>53.62106425908989</v>
-      </c>
-      <c r="K19" t="n">
-        <v>476.51761297741</v>
-      </c>
-      <c r="L19" t="n">
-        <v>52.08247826376749</v>
-      </c>
-      <c r="M19" t="n">
-        <v>476.4152462035376</v>
-      </c>
-      <c r="N19" t="n">
-        <v>52.68913410848486</v>
-      </c>
-      <c r="O19" t="n">
-        <v>467.8150057645991</v>
-      </c>
-      <c r="P19" t="n">
-        <v>58.33187991646908</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>469.8631464150514</v>
-      </c>
       <c r="R19" t="n">
-        <v>55.43470375422773</v>
+        <v>476.3</v>
       </c>
       <c r="S19" t="n">
-        <v>467.3893849719543</v>
+        <v>68.87</v>
       </c>
       <c r="T19" t="n">
-        <v>49.29549430692958</v>
+        <v>475.12</v>
       </c>
       <c r="U19" t="n">
-        <v>471.7459265749216</v>
+        <v>58.3</v>
       </c>
       <c r="V19" t="n">
-        <v>48.44759797993741</v>
+        <v>482.74</v>
       </c>
       <c r="W19" t="n">
-        <v>471.13111187763</v>
+        <v>55.88</v>
       </c>
       <c r="X19" t="n">
-        <v>49.14820251467398</v>
+        <v>479.17</v>
       </c>
       <c r="Y19" t="n">
-        <v>470.3150908229713</v>
+        <v>56.91</v>
       </c>
       <c r="Z19" t="n">
-        <v>52.23494912783119</v>
+        <v>479.22</v>
       </c>
       <c r="AA19" t="n">
-        <v>-0.2</v>
+        <v>56.61</v>
       </c>
       <c r="AB19" t="n">
+        <v>476.5</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>50.43</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>483.21</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>49.98</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>481.91</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>49.86</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>474.7</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>50.82</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>-0.2666666666666667</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>-0.125</v>
+      </c>
+      <c r="AM19" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AC19" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>-0.1069182389937107</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>-0.0898876404494382</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>-0.09090909090909091</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>465.625</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>470.9166666666667</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>472.6</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>470.1</v>
-      </c>
       <c r="AN19" t="n">
-        <v>469.65</v>
+        <v>-0.08333333333333333</v>
       </c>
       <c r="AO19" t="n">
-        <v>470.3428571428572</v>
+        <v>-0.01428571428571429</v>
       </c>
       <c r="AP19" t="n">
-        <v>470.125</v>
+        <v>-0.05</v>
       </c>
       <c r="AQ19" t="n">
-        <v>470.7555555555555</v>
+        <v>-0.04444444444444445</v>
       </c>
       <c r="AR19" t="n">
-        <v>470.11</v>
+        <v>-0.03</v>
       </c>
       <c r="AS19" t="n">
-        <v>55.65010669351857</v>
+        <v>464.1</v>
       </c>
       <c r="AT19" t="n">
-        <v>53.56967166431228</v>
+        <v>474.8166666666667</v>
       </c>
       <c r="AU19" t="n">
-        <v>53.16615464748227</v>
+        <v>481.5125</v>
       </c>
       <c r="AV19" t="n">
-        <v>54.75792180132478</v>
+        <v>480.74</v>
       </c>
       <c r="AW19" t="n">
-        <v>56.56996405631997</v>
+        <v>480.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>55.44350682433058</v>
+        <v>481.75</v>
       </c>
       <c r="AY19" t="n">
-        <v>54.0691397656741</v>
+        <v>479.55</v>
       </c>
       <c r="AZ19" t="n">
-        <v>52.73651720500303</v>
+        <v>479.9555555555556</v>
       </c>
       <c r="BA19" t="n">
-        <v>52.48797862368106</v>
+        <v>479.855</v>
       </c>
       <c r="BB19" t="n">
-        <v>360</v>
+        <v>43.8</v>
       </c>
       <c r="BC19" t="n">
-        <v>360</v>
+        <v>57.04106464254989</v>
       </c>
       <c r="BD19" t="n">
-        <v>360</v>
+        <v>61.35694617359961</v>
       </c>
       <c r="BE19" t="n">
-        <v>360</v>
+        <v>60.6426615510896</v>
       </c>
       <c r="BF19" t="n">
-        <v>360</v>
+        <v>60.72286774079981</v>
       </c>
       <c r="BG19" t="n">
-        <v>360</v>
+        <v>58.48004849030626</v>
       </c>
       <c r="BH19" t="n">
-        <v>360</v>
+        <v>56.82877792104982</v>
       </c>
       <c r="BI19" t="n">
-        <v>360</v>
+        <v>55.67403366643519</v>
       </c>
       <c r="BJ19" t="n">
-        <v>360</v>
+        <v>54.64488974277467</v>
       </c>
       <c r="BK19" t="n">
-        <v>539</v>
+        <v>368</v>
       </c>
       <c r="BL19" t="n">
-        <v>539</v>
+        <v>368</v>
       </c>
       <c r="BM19" t="n">
-        <v>545</v>
+        <v>368</v>
       </c>
       <c r="BN19" t="n">
-        <v>546</v>
+        <v>368</v>
       </c>
       <c r="BO19" t="n">
-        <v>546</v>
+        <v>368</v>
       </c>
       <c r="BP19" t="n">
-        <v>546</v>
+        <v>368</v>
       </c>
       <c r="BQ19" t="n">
-        <v>546</v>
+        <v>368</v>
       </c>
       <c r="BR19" t="n">
-        <v>546</v>
+        <v>368</v>
       </c>
       <c r="BS19" t="n">
-        <v>546</v>
+        <v>368</v>
       </c>
       <c r="BT19" t="n">
+        <v>541</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>564</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>572</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>572</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>572</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>572</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>572</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>572</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>572</v>
+      </c>
+      <c r="CC19" t="n">
         <v>1</v>
       </c>
-      <c r="BU19" t="n">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="BV19" t="n">
-        <v>0.8461538461538461</v>
-      </c>
-      <c r="BW19" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BX19" t="n">
-        <v>0.7647058823529411</v>
-      </c>
-      <c r="BY19" t="n">
+      <c r="CD19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG19" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="CH19" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="CI19" t="n">
         <v>0.95</v>
       </c>
-      <c r="BZ19" t="n">
-        <v>0.9523809523809523</v>
-      </c>
-      <c r="CA19" t="n">
-        <v>0.9583333333333334</v>
-      </c>
-      <c r="CB19" t="n">
-        <v>0.9</v>
+      <c r="CJ19" t="n">
+        <v>0.9565217391304348</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>0.9615384615384616</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>474.7</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>50.82</v>
       </c>
     </row>
     <row r="20">
@@ -5268,10 +5917,10 @@
         <v>480</v>
       </c>
       <c r="C20" t="n">
+        <v>57.82060785767235</v>
+      </c>
+      <c r="D20" t="n">
         <v>39</v>
-      </c>
-      <c r="D20" t="n">
-        <v>57.82060785767235</v>
       </c>
       <c r="E20" t="n">
         <v>480</v>
@@ -5280,228 +5929,261 @@
         <v>200</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H20" t="inlineStr">
+        <v>75</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>465.7994383378681</v>
-      </c>
-      <c r="J20" t="n">
-        <v>40.04387379861956</v>
-      </c>
-      <c r="K20" t="n">
-        <v>475.5604127797148</v>
-      </c>
-      <c r="L20" t="n">
-        <v>33.44034159358475</v>
-      </c>
-      <c r="M20" t="n">
-        <v>482.9157221504807</v>
-      </c>
-      <c r="N20" t="n">
-        <v>37.04225713315262</v>
-      </c>
-      <c r="O20" t="n">
-        <v>481.4497852043688</v>
-      </c>
-      <c r="P20" t="n">
-        <v>37.25805887173229</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>486.4318572245225</v>
-      </c>
       <c r="R20" t="n">
-        <v>36.51271383129294</v>
+        <v>465.8</v>
       </c>
       <c r="S20" t="n">
-        <v>490.0303922942543</v>
+        <v>40.04</v>
       </c>
       <c r="T20" t="n">
-        <v>42.34666866155729</v>
+        <v>475.56</v>
       </c>
       <c r="U20" t="n">
-        <v>486.3589421341296</v>
+        <v>33.44</v>
       </c>
       <c r="V20" t="n">
-        <v>44.99725317684366</v>
+        <v>482.92</v>
       </c>
       <c r="W20" t="n">
-        <v>483.5419602771123</v>
+        <v>37.04</v>
       </c>
       <c r="X20" t="n">
-        <v>47.22674778904283</v>
+        <v>481.45</v>
       </c>
       <c r="Y20" t="n">
-        <v>481.8986140597958</v>
+        <v>37.26</v>
       </c>
       <c r="Z20" t="n">
-        <v>47.29966868632772</v>
+        <v>486.43</v>
       </c>
       <c r="AA20" t="n">
+        <v>36.51</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>490.03</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>42.35</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>486.36</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>45</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>483.54</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>47.23</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>481.9</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>-0.5897435897435898</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AK20" t="n">
         <v>-0.5254237288135594</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AL20" t="n">
         <v>-0.3924050632911392</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AM20" t="n">
         <v>-0.2727272727272727</v>
       </c>
-      <c r="AE20" t="n">
+      <c r="AN20" t="n">
         <v>-0.226890756302521</v>
       </c>
-      <c r="AF20" t="n">
+      <c r="AO20" t="n">
         <v>-0.1223021582733813</v>
       </c>
-      <c r="AG20" t="n">
+      <c r="AP20" t="n">
         <v>-0.1320754716981132</v>
       </c>
-      <c r="AH20" t="n">
+      <c r="AQ20" t="n">
         <v>-0.1173184357541899</v>
       </c>
-      <c r="AI20" t="n">
+      <c r="AR20" t="n">
         <v>-0.1155778894472362</v>
       </c>
-      <c r="AJ20" t="n">
+      <c r="AS20" t="n">
         <v>460.4</v>
       </c>
-      <c r="AK20" t="n">
+      <c r="AT20" t="n">
         <v>462.2166666666666</v>
       </c>
-      <c r="AL20" t="n">
+      <c r="AU20" t="n">
         <v>469.75</v>
       </c>
-      <c r="AM20" t="n">
+      <c r="AV20" t="n">
         <v>473.74</v>
       </c>
-      <c r="AN20" t="n">
+      <c r="AW20" t="n">
         <v>475.9166666666667</v>
       </c>
-      <c r="AO20" t="n">
+      <c r="AX20" t="n">
         <v>481.2071428571429</v>
       </c>
-      <c r="AP20" t="n">
+      <c r="AY20" t="n">
         <v>481.1125</v>
       </c>
-      <c r="AQ20" t="n">
+      <c r="AZ20" t="n">
         <v>482.1166666666667</v>
       </c>
-      <c r="AR20" t="n">
+      <c r="BA20" t="n">
         <v>481.695</v>
       </c>
-      <c r="AS20" t="n">
+      <c r="BB20" t="n">
         <v>46.10466353851853</v>
       </c>
-      <c r="AT20" t="n">
+      <c r="BC20" t="n">
         <v>42.88204428688332</v>
       </c>
-      <c r="AU20" t="n">
+      <c r="BD20" t="n">
         <v>42.5718510285846</v>
       </c>
-      <c r="AV20" t="n">
+      <c r="BE20" t="n">
         <v>41.54073181830094</v>
       </c>
-      <c r="AW20" t="n">
+      <c r="BF20" t="n">
         <v>42.01558903814418</v>
       </c>
-      <c r="AX20" t="n">
+      <c r="BG20" t="n">
         <v>43.18903571651547</v>
       </c>
-      <c r="AY20" t="n">
+      <c r="BH20" t="n">
         <v>43.43817265666225</v>
       </c>
-      <c r="AZ20" t="n">
+      <c r="BI20" t="n">
         <v>44.71207579862763</v>
       </c>
-      <c r="BA20" t="n">
+      <c r="BJ20" t="n">
         <v>45.24767369710845</v>
       </c>
-      <c r="BB20" t="n">
+      <c r="BK20" t="n">
         <v>348</v>
       </c>
-      <c r="BC20" t="n">
+      <c r="BL20" t="n">
         <v>348</v>
       </c>
-      <c r="BD20" t="n">
+      <c r="BM20" t="n">
         <v>348</v>
       </c>
-      <c r="BE20" t="n">
+      <c r="BN20" t="n">
         <v>348</v>
       </c>
-      <c r="BF20" t="n">
+      <c r="BO20" t="n">
         <v>348</v>
       </c>
-      <c r="BG20" t="n">
+      <c r="BP20" t="n">
         <v>348</v>
       </c>
-      <c r="BH20" t="n">
+      <c r="BQ20" t="n">
         <v>348</v>
       </c>
-      <c r="BI20" t="n">
+      <c r="BR20" t="n">
         <v>348</v>
       </c>
-      <c r="BJ20" t="n">
+      <c r="BS20" t="n">
         <v>348</v>
       </c>
-      <c r="BK20" t="n">
+      <c r="BT20" t="n">
         <v>530</v>
       </c>
-      <c r="BL20" t="n">
+      <c r="BU20" t="n">
         <v>530</v>
       </c>
-      <c r="BM20" t="n">
+      <c r="BV20" t="n">
         <v>539</v>
       </c>
-      <c r="BN20" t="n">
+      <c r="BW20" t="n">
         <v>539</v>
       </c>
-      <c r="BO20" t="n">
+      <c r="BX20" t="n">
         <v>546</v>
       </c>
-      <c r="BP20" t="n">
+      <c r="BY20" t="n">
         <v>550</v>
       </c>
-      <c r="BQ20" t="n">
+      <c r="BZ20" t="n">
         <v>550</v>
       </c>
-      <c r="BR20" t="n">
+      <c r="CA20" t="n">
         <v>554</v>
       </c>
-      <c r="BS20" t="n">
+      <c r="CB20" t="n">
         <v>554</v>
       </c>
-      <c r="BT20" t="n">
+      <c r="CC20" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BU20" t="n">
+      <c r="CD20" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="BV20" t="n">
+      <c r="CE20" t="n">
         <v>0.75</v>
       </c>
-      <c r="BW20" t="n">
+      <c r="CF20" t="n">
         <v>1</v>
       </c>
-      <c r="BX20" t="n">
+      <c r="CG20" t="n">
         <v>0.1875</v>
       </c>
-      <c r="BY20" t="n">
+      <c r="CH20" t="n">
         <v>0.9047619047619048</v>
       </c>
-      <c r="BZ20" t="n">
+      <c r="CI20" t="n">
         <v>0.9565217391304348</v>
       </c>
-      <c r="CA20" t="n">
+      <c r="CJ20" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="CB20" t="n">
+      <c r="CK20" t="n">
         <v>0.8928571428571429</v>
+      </c>
+      <c r="CL20" t="n">
+        <v>481.9</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>47.3</v>
       </c>
     </row>
     <row r="21">
@@ -5514,10 +6196,10 @@
         <v>479</v>
       </c>
       <c r="C21" t="n">
+        <v>59.30318754633062</v>
+      </c>
+      <c r="D21" t="n">
         <v>40</v>
-      </c>
-      <c r="D21" t="n">
-        <v>59.30318754633062</v>
       </c>
       <c r="E21" t="n">
         <v>479</v>
@@ -5526,228 +6208,261 @@
         <v>200</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H21" t="inlineStr">
+        <v>76</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>478.4046918798007</v>
-      </c>
-      <c r="J21" t="n">
-        <v>51.41338296692881</v>
-      </c>
-      <c r="K21" t="n">
-        <v>477.0956654411659</v>
-      </c>
-      <c r="L21" t="n">
-        <v>50.5878821241857</v>
-      </c>
-      <c r="M21" t="n">
-        <v>476.4277139912315</v>
-      </c>
-      <c r="N21" t="n">
-        <v>47.08749295498628</v>
-      </c>
-      <c r="O21" t="n">
-        <v>477.4899350173125</v>
-      </c>
-      <c r="P21" t="n">
-        <v>47.78253355394972</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>475.0306850649797</v>
-      </c>
       <c r="R21" t="n">
-        <v>48.83987513930776</v>
+        <v>478.4</v>
       </c>
       <c r="S21" t="n">
-        <v>476.6738928161602</v>
+        <v>51.41</v>
       </c>
       <c r="T21" t="n">
-        <v>46.25522850366023</v>
+        <v>477.1</v>
       </c>
       <c r="U21" t="n">
-        <v>480.5390615773903</v>
+        <v>50.59</v>
       </c>
       <c r="V21" t="n">
-        <v>48.94707535697695</v>
+        <v>476.43</v>
       </c>
       <c r="W21" t="n">
-        <v>480.7982437580223</v>
+        <v>47.09</v>
       </c>
       <c r="X21" t="n">
-        <v>50.68237010937661</v>
+        <v>477.49</v>
       </c>
       <c r="Y21" t="n">
-        <v>478.5777324939246</v>
+        <v>47.78</v>
       </c>
       <c r="Z21" t="n">
-        <v>50.02403558950587</v>
+        <v>475.03</v>
       </c>
       <c r="AA21" t="n">
+        <v>48.84</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>476.67</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>46.26</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>480.54</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>48.95</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>480.8</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>50.68</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>478.58</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>50.02</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>-0.15</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AK21" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AL21" t="n">
         <v>-0.075</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AM21" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AE21" t="n">
+      <c r="AN21" t="n">
         <v>-0.03333333333333333</v>
       </c>
-      <c r="AF21" t="n">
+      <c r="AO21" t="n">
         <v>-0.02857142857142857</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AP21" t="n">
         <v>-0.025</v>
       </c>
-      <c r="AH21" t="n">
+      <c r="AQ21" t="n">
         <v>0</v>
       </c>
-      <c r="AI21" t="n">
+      <c r="AR21" t="n">
         <v>0</v>
       </c>
-      <c r="AJ21" t="n">
+      <c r="AS21" t="n">
         <v>478.55</v>
       </c>
-      <c r="AK21" t="n">
+      <c r="AT21" t="n">
         <v>477.1833333333333</v>
       </c>
-      <c r="AL21" t="n">
+      <c r="AU21" t="n">
         <v>476.5375</v>
       </c>
-      <c r="AM21" t="n">
+      <c r="AV21" t="n">
         <v>477.17</v>
       </c>
-      <c r="AN21" t="n">
+      <c r="AW21" t="n">
         <v>476.6416666666667</v>
       </c>
-      <c r="AO21" t="n">
+      <c r="AX21" t="n">
         <v>476.5142857142857</v>
       </c>
-      <c r="AP21" t="n">
+      <c r="AY21" t="n">
         <v>476.4</v>
       </c>
-      <c r="AQ21" t="n">
+      <c r="AZ21" t="n">
         <v>478.0055555555555</v>
       </c>
-      <c r="AR21" t="n">
+      <c r="BA21" t="n">
         <v>478.24</v>
       </c>
-      <c r="AS21" t="n">
+      <c r="BB21" t="n">
         <v>50.36514171527764</v>
       </c>
-      <c r="AT21" t="n">
+      <c r="BC21" t="n">
         <v>53.21731913160937</v>
       </c>
-      <c r="AU21" t="n">
+      <c r="BD21" t="n">
         <v>52.57469537477131</v>
       </c>
-      <c r="AV21" t="n">
+      <c r="BE21" t="n">
         <v>51.46320141615755</v>
       </c>
-      <c r="AW21" t="n">
+      <c r="BF21" t="n">
         <v>50.53246412511026</v>
       </c>
-      <c r="AX21" t="n">
+      <c r="BG21" t="n">
         <v>49.58016390716376</v>
       </c>
-      <c r="AY21" t="n">
+      <c r="BH21" t="n">
         <v>48.7229668636876</v>
       </c>
-      <c r="AZ21" t="n">
+      <c r="BI21" t="n">
         <v>49.35354284504837</v>
       </c>
-      <c r="BA21" t="n">
+      <c r="BJ21" t="n">
         <v>49.2124211962793</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BK21" t="n">
         <v>348</v>
       </c>
-      <c r="BC21" t="n">
+      <c r="BL21" t="n">
         <v>348</v>
       </c>
-      <c r="BD21" t="n">
+      <c r="BM21" t="n">
         <v>348</v>
       </c>
-      <c r="BE21" t="n">
+      <c r="BN21" t="n">
         <v>348</v>
       </c>
-      <c r="BF21" t="n">
+      <c r="BO21" t="n">
         <v>348</v>
       </c>
-      <c r="BG21" t="n">
+      <c r="BP21" t="n">
         <v>348</v>
       </c>
-      <c r="BH21" t="n">
+      <c r="BQ21" t="n">
         <v>348</v>
       </c>
-      <c r="BI21" t="n">
+      <c r="BR21" t="n">
         <v>348</v>
       </c>
-      <c r="BJ21" t="n">
+      <c r="BS21" t="n">
         <v>348</v>
       </c>
-      <c r="BK21" t="n">
+      <c r="BT21" t="n">
         <v>558</v>
       </c>
-      <c r="BL21" t="n">
+      <c r="BU21" t="n">
         <v>558</v>
       </c>
-      <c r="BM21" t="n">
+      <c r="BV21" t="n">
         <v>558</v>
       </c>
-      <c r="BN21" t="n">
+      <c r="BW21" t="n">
         <v>558</v>
       </c>
-      <c r="BO21" t="n">
+      <c r="BX21" t="n">
         <v>558</v>
       </c>
-      <c r="BP21" t="n">
+      <c r="BY21" t="n">
         <v>558</v>
       </c>
-      <c r="BQ21" t="n">
+      <c r="BZ21" t="n">
         <v>558</v>
       </c>
-      <c r="BR21" t="n">
+      <c r="CA21" t="n">
         <v>558</v>
       </c>
-      <c r="BS21" t="n">
+      <c r="CB21" t="n">
         <v>558</v>
       </c>
-      <c r="BT21" t="n">
+      <c r="CC21" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BU21" t="n">
+      <c r="CD21" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="BV21" t="n">
+      <c r="CE21" t="n">
         <v>0</v>
       </c>
-      <c r="BW21" t="n">
+      <c r="CF21" t="n">
         <v>0.9285714285714286</v>
       </c>
-      <c r="BX21" t="n">
+      <c r="CG21" t="n">
         <v>0.9411764705882353</v>
       </c>
-      <c r="BY21" t="n">
+      <c r="CH21" t="n">
         <v>0.9047619047619048</v>
       </c>
-      <c r="BZ21" t="n">
+      <c r="CI21" t="n">
         <v>0</v>
       </c>
-      <c r="CA21" t="n">
+      <c r="CJ21" t="n">
         <v>1</v>
       </c>
-      <c r="CB21" t="n">
+      <c r="CK21" t="n">
         <v>1</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>478.58</v>
+      </c>
+      <c r="CM21" t="n">
+        <v>50.02</v>
       </c>
     </row>
     <row r="22">
@@ -5760,10 +6475,10 @@
         <v>479.95</v>
       </c>
       <c r="C22" t="n">
+        <v>59.45144551519644</v>
+      </c>
+      <c r="D22" t="n">
         <v>40.1</v>
-      </c>
-      <c r="D22" t="n">
-        <v>59.45144551519644</v>
       </c>
       <c r="E22" t="n">
         <v>479.95</v>
@@ -5772,224 +6487,239 @@
         <v>200</v>
       </c>
       <c r="G22" t="n">
-        <v>0.49925</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>74.5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.795</v>
+      </c>
       <c r="I22" t="n">
-        <v>472.5613042941561</v>
+        <v>2.774</v>
       </c>
       <c r="J22" t="n">
-        <v>43.86033347452384</v>
+        <v>2.747</v>
       </c>
       <c r="K22" t="n">
-        <v>476.4282616368985</v>
+        <v>2.724000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>45.71223897056161</v>
+        <v>2.702</v>
       </c>
       <c r="M22" t="n">
-        <v>477.8060187337347</v>
+        <v>2.6755</v>
       </c>
       <c r="N22" t="n">
-        <v>44.08718476737392</v>
+        <v>2.794999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>479.2370972251293</v>
+        <v>2.844</v>
       </c>
       <c r="P22" t="n">
-        <v>45.12042520421434</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>478.0863830419419</v>
-      </c>
+        <v>2.839</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>45.82695685363564</v>
+        <v>472.5599999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>478.3317218071044</v>
+        <v>43.8595</v>
       </c>
       <c r="T22" t="n">
-        <v>46.60051953899891</v>
+        <v>476.429</v>
       </c>
       <c r="U22" t="n">
-        <v>478.5506244125486</v>
+        <v>45.711</v>
       </c>
       <c r="V22" t="n">
-        <v>46.81687156921092</v>
+        <v>477.8065</v>
       </c>
       <c r="W22" t="n">
-        <v>478.9962247773536</v>
+        <v>44.0875</v>
       </c>
       <c r="X22" t="n">
-        <v>46.87180092254978</v>
+        <v>479.2375</v>
       </c>
       <c r="Y22" t="n">
-        <v>478.5251721389812</v>
+        <v>45.121</v>
       </c>
       <c r="Z22" t="n">
-        <v>46.72484290409135</v>
+        <v>478.0860000000001</v>
       </c>
       <c r="AA22" t="n">
-        <v>-0.3859514170040486</v>
+        <v>45.8265</v>
       </c>
       <c r="AB22" t="n">
-        <v>-0.2851315020455873</v>
+        <v>478.3320000000001</v>
       </c>
       <c r="AC22" t="n">
-        <v>-0.2305643459915612</v>
+        <v>46.6005</v>
       </c>
       <c r="AD22" t="n">
-        <v>-0.2079688723974438</v>
+        <v>478.5505000000001</v>
       </c>
       <c r="AE22" t="n">
-        <v>-0.1942112210167527</v>
+        <v>46.8175</v>
       </c>
       <c r="AF22" t="n">
-        <v>-0.1699720434762975</v>
+        <v>478.996</v>
       </c>
       <c r="AG22" t="n">
-        <v>-0.1488516599747763</v>
+        <v>46.8725</v>
       </c>
       <c r="AH22" t="n">
-        <v>-0.1368012375042813</v>
+        <v>478.5245</v>
       </c>
       <c r="AI22" t="n">
-        <v>-0.1305917925908524</v>
+        <v>46.7245</v>
       </c>
       <c r="AJ22" t="n">
-        <v>471.6612499999999</v>
+        <v>-0.3855</v>
       </c>
       <c r="AK22" t="n">
-        <v>474.7883333333333</v>
+        <v>-0.284</v>
       </c>
       <c r="AL22" t="n">
-        <v>476.29375</v>
+        <v>-0.23</v>
       </c>
       <c r="AM22" t="n">
+        <v>-0.2075</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>-0.1945</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>-0.137</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>-0.1315</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>471.6609999999999</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>474.7889999999999</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>476.2945000000001</v>
+      </c>
+      <c r="AV22" t="n">
         <v>477.0495</v>
       </c>
-      <c r="AN22" t="n">
-        <v>477.0820833333333</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>477.6171428571429</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>478.0831249999999</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>478.2683333333333</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>478.22725</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>46.35533117231807</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>49.39789238686878</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>49.94964927236031</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>49.25946195511247</v>
-      </c>
       <c r="AW22" t="n">
-        <v>49.10439838903829</v>
+        <v>477.0814999999999</v>
       </c>
       <c r="AX22" t="n">
-        <v>48.91948796534967</v>
+        <v>477.6165</v>
       </c>
       <c r="AY22" t="n">
-        <v>48.98199986432105</v>
+        <v>478.0825</v>
       </c>
       <c r="AZ22" t="n">
-        <v>48.86330648495902</v>
+        <v>478.2695000000001</v>
       </c>
       <c r="BA22" t="n">
-        <v>48.63134137717361</v>
+        <v>478.2265</v>
       </c>
       <c r="BB22" t="n">
+        <v>46.3545</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>49.397</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>49.9495</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>49.2595</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>49.1045</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>48.919</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>48.98200000000001</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>48.8635</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>48.6315</v>
+      </c>
+      <c r="BK22" t="n">
         <v>362.9</v>
       </c>
-      <c r="BC22" t="n">
+      <c r="BL22" t="n">
         <v>362.3</v>
       </c>
-      <c r="BD22" t="n">
+      <c r="BM22" t="n">
         <v>361.85</v>
       </c>
-      <c r="BE22" t="n">
+      <c r="BN22" t="n">
         <v>361.85</v>
       </c>
-      <c r="BF22" t="n">
+      <c r="BO22" t="n">
         <v>361.85</v>
       </c>
-      <c r="BG22" t="n">
+      <c r="BP22" t="n">
         <v>361.85</v>
       </c>
-      <c r="BH22" t="n">
+      <c r="BQ22" t="n">
         <v>361.85</v>
       </c>
-      <c r="BI22" t="n">
+      <c r="BR22" t="n">
         <v>361.85</v>
       </c>
-      <c r="BJ22" t="n">
+      <c r="BS22" t="n">
         <v>361.85</v>
       </c>
-      <c r="BK22" t="n">
+      <c r="BT22" t="n">
         <v>568.75</v>
       </c>
-      <c r="BL22" t="n">
+      <c r="BU22" t="n">
         <v>576.45</v>
       </c>
-      <c r="BM22" t="n">
+      <c r="BV22" t="n">
         <v>579.85</v>
       </c>
-      <c r="BN22" t="n">
+      <c r="BW22" t="n">
         <v>579.9</v>
       </c>
-      <c r="BO22" t="n">
+      <c r="BX22" t="n">
         <v>580.35</v>
       </c>
-      <c r="BP22" t="n">
+      <c r="BY22" t="n">
         <v>580.85</v>
       </c>
-      <c r="BQ22" t="n">
+      <c r="BZ22" t="n">
         <v>581.4</v>
       </c>
-      <c r="BR22" t="n">
+      <c r="CA22" t="n">
         <v>581.6</v>
       </c>
-      <c r="BS22" t="n">
+      <c r="CB22" t="n">
         <v>581.6</v>
       </c>
-      <c r="BT22" t="n">
-        <v>0.6903841991341992</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>0.7445980408480408</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>0.7423261338334868</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>0.8230694264885441</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>0.7534763267348407</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>0.8186352914650568</v>
-      </c>
-      <c r="BZ22" t="n">
-        <v>0.740722737800135</v>
-      </c>
-      <c r="CA22" t="n">
-        <v>0.83474041305528</v>
-      </c>
-      <c r="CB22" t="n">
-        <v>0.7779124573285447</v>
+      <c r="CC22" t="inlineStr"/>
+      <c r="CD22" t="inlineStr"/>
+      <c r="CE22" t="inlineStr"/>
+      <c r="CF22" t="inlineStr"/>
+      <c r="CG22" t="inlineStr"/>
+      <c r="CH22" t="inlineStr"/>
+      <c r="CI22" t="inlineStr"/>
+      <c r="CJ22" t="inlineStr"/>
+      <c r="CK22" t="inlineStr"/>
+      <c r="CL22" t="n">
+        <v>478.5245</v>
+      </c>
+      <c r="CM22" t="n">
+        <v>46.7245</v>
       </c>
     </row>
     <row r="23">
@@ -6002,10 +6732,10 @@
         <v>1.316894273021107</v>
       </c>
       <c r="C23" t="n">
+        <v>2.199021048805233</v>
+      </c>
+      <c r="D23" t="n">
         <v>1.483239697419132</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2.199021048805233</v>
       </c>
       <c r="E23" t="n">
         <v>1.316894273021107</v>
@@ -6014,224 +6744,239 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01955256074223905</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>3.008759142727674</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.174491743131452</v>
+      </c>
       <c r="I23" t="n">
-        <v>13.42595004462213</v>
+        <v>0.1608660770232248</v>
       </c>
       <c r="J23" t="n">
-        <v>16.37388470945931</v>
+        <v>0.1645440270629878</v>
       </c>
       <c r="K23" t="n">
-        <v>12.30151369285095</v>
+        <v>0.1774201080397656</v>
       </c>
       <c r="L23" t="n">
-        <v>12.08930698732817</v>
+        <v>0.1924523180864343</v>
       </c>
       <c r="M23" t="n">
-        <v>10.42451810684411</v>
+        <v>0.1937300074574759</v>
       </c>
       <c r="N23" t="n">
-        <v>10.58739666905284</v>
+        <v>0.3084170109309454</v>
       </c>
       <c r="O23" t="n">
-        <v>11.65795135104603</v>
+        <v>0.193918051058471</v>
       </c>
       <c r="P23" t="n">
-        <v>9.833123818105493</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>10.06391843011088</v>
-      </c>
+        <v>0.1757659927589132</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>8.594814950584942</v>
+        <v>13.42553654715323</v>
       </c>
       <c r="S23" t="n">
-        <v>8.688701898564437</v>
+        <v>16.37236518778229</v>
       </c>
       <c r="T23" t="n">
-        <v>6.899008714981697</v>
+        <v>12.30204129402922</v>
       </c>
       <c r="U23" t="n">
-        <v>8.641250754210406</v>
+        <v>12.08989917680305</v>
       </c>
       <c r="V23" t="n">
-        <v>6.314137972576908</v>
+        <v>10.42486060742352</v>
       </c>
       <c r="W23" t="n">
-        <v>8.945116423140227</v>
+        <v>10.58765908971383</v>
       </c>
       <c r="X23" t="n">
-        <v>6.007792910279852</v>
+        <v>11.65802135193212</v>
       </c>
       <c r="Y23" t="n">
-        <v>8.594396192472182</v>
+        <v>9.83396311393915</v>
       </c>
       <c r="Z23" t="n">
-        <v>6.075878647721416</v>
+        <v>10.0646899186162</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.3183263823497903</v>
+        <v>8.594524741154439</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.2563137337528004</v>
+        <v>8.688937067813356</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.2237551710704218</v>
+        <v>6.89942825625123</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.2231780527621139</v>
+        <v>8.642367167805235</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.2113139739046425</v>
+        <v>6.313463370990767</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.1686939907641382</v>
+        <v>8.94494823614807</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.1395128739415749</v>
+        <v>6.007538137513921</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.1369104262224417</v>
+        <v>8.59342066258894</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.1350667863339081</v>
+        <v>6.074609344164488</v>
       </c>
       <c r="AJ23" t="n">
-        <v>15.66842171837154</v>
+        <v>0.3184249891013746</v>
       </c>
       <c r="AK23" t="n">
-        <v>14.15194704848622</v>
+        <v>0.2556395488717824</v>
       </c>
       <c r="AL23" t="n">
-        <v>12.29370860975559</v>
+        <v>0.2244056477382913</v>
       </c>
       <c r="AM23" t="n">
+        <v>0.223132601595412</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0.2106000199930015</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0.168679078664034</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0.1398871725807323</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0.1361539376472164</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0.1348400612031275</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>15.66937405124706</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>14.15085115535643</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>12.2937893926803</v>
+      </c>
+      <c r="AV23" t="n">
         <v>11.91036323410924</v>
       </c>
-      <c r="AN23" t="n">
-        <v>11.35322148005342</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>10.29779532785504</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>9.554373933777518</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>9.581166057163658</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>9.310199624039953</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>12.34441289152883</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>10.89711212142458</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>9.901036133615122</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>9.525342535232109</v>
-      </c>
       <c r="AW23" t="n">
-        <v>8.822521923371129</v>
+        <v>11.35386846896363</v>
       </c>
       <c r="AX23" t="n">
-        <v>7.804744161899521</v>
+        <v>10.29833725720603</v>
       </c>
       <c r="AY23" t="n">
-        <v>6.94177069197028</v>
+        <v>9.554522695947105</v>
       </c>
       <c r="AZ23" t="n">
-        <v>6.19741727412131</v>
+        <v>9.581106668856158</v>
       </c>
       <c r="BA23" t="n">
-        <v>5.790683725360998</v>
+        <v>9.310711022088597</v>
       </c>
       <c r="BB23" t="n">
+        <v>12.34369025901599</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>10.89775935444385</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>9.902200964804161</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>9.525179083825531</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>8.821385781455382</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>7.804088604530858</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>6.942047021023789</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>6.195945427200122</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>5.79147674559234</v>
+      </c>
+      <c r="BK23" t="n">
         <v>32.56879358817999</v>
       </c>
-      <c r="BC23" t="n">
+      <c r="BL23" t="n">
         <v>31.05190900140568</v>
       </c>
-      <c r="BD23" t="n">
+      <c r="BM23" t="n">
         <v>30.02152736392934</v>
       </c>
-      <c r="BE23" t="n">
+      <c r="BN23" t="n">
         <v>30.02152736392934</v>
       </c>
-      <c r="BF23" t="n">
+      <c r="BO23" t="n">
         <v>30.02152736392934</v>
       </c>
-      <c r="BG23" t="n">
+      <c r="BP23" t="n">
         <v>30.02152736392934</v>
       </c>
-      <c r="BH23" t="n">
+      <c r="BQ23" t="n">
         <v>30.02152736392934</v>
       </c>
-      <c r="BI23" t="n">
+      <c r="BR23" t="n">
         <v>30.02152736392934</v>
       </c>
-      <c r="BJ23" t="n">
+      <c r="BS23" t="n">
         <v>30.02152736392934</v>
       </c>
-      <c r="BK23" t="n">
+      <c r="BT23" t="n">
         <v>49.58976443624335</v>
       </c>
-      <c r="BL23" t="n">
+      <c r="BU23" t="n">
         <v>44.01372393625472</v>
       </c>
-      <c r="BM23" t="n">
-        <v>41.89997487752042</v>
-      </c>
-      <c r="BN23" t="n">
+      <c r="BV23" t="n">
+        <v>41.89997487752041</v>
+      </c>
+      <c r="BW23" t="n">
         <v>41.8567733310179</v>
       </c>
-      <c r="BO23" t="n">
+      <c r="BX23" t="n">
         <v>41.44022327718756</v>
       </c>
-      <c r="BP23" t="n">
-        <v>40.91618519029256</v>
-      </c>
-      <c r="BQ23" t="n">
+      <c r="BY23" t="n">
+        <v>40.91618519029255</v>
+      </c>
+      <c r="BZ23" t="n">
         <v>40.66991646491493</v>
       </c>
-      <c r="BR23" t="n">
+      <c r="CA23" t="n">
         <v>40.51692304002834</v>
       </c>
-      <c r="BS23" t="n">
+      <c r="CB23" t="n">
         <v>40.51692304002834</v>
       </c>
-      <c r="BT23" t="n">
-        <v>0.3035415837693299</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>0.1638031343899188</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>0.2784635283006874</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>0.167555782387594</v>
-      </c>
-      <c r="BX23" t="n">
-        <v>0.2380056028843169</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>0.1735945228634363</v>
-      </c>
-      <c r="BZ23" t="n">
-        <v>0.3036475216823283</v>
-      </c>
-      <c r="CA23" t="n">
-        <v>0.2102224651973363</v>
-      </c>
-      <c r="CB23" t="n">
-        <v>0.3101207952353475</v>
+      <c r="CC23" t="inlineStr"/>
+      <c r="CD23" t="inlineStr"/>
+      <c r="CE23" t="inlineStr"/>
+      <c r="CF23" t="inlineStr"/>
+      <c r="CG23" t="inlineStr"/>
+      <c r="CH23" t="inlineStr"/>
+      <c r="CI23" t="inlineStr"/>
+      <c r="CJ23" t="inlineStr"/>
+      <c r="CK23" t="inlineStr"/>
+      <c r="CL23" t="n">
+        <v>8.59342066258894</v>
+      </c>
+      <c r="CM23" t="n">
+        <v>6.074609344164488</v>
       </c>
     </row>
   </sheetData>
